--- a/template/TOPOLOGY TEMPLATE.xlsx
+++ b/template/TOPOLOGY TEMPLATE.xlsx
@@ -10,14 +10,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="READ ME" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NODES" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SPURS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BENDS" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EXAMPLE" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMU WAYS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BENDS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EXAMPLE" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'NODES'!$A$1:$N$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'NODES'!$A$1:$O$129</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'NODES'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SPURS'!$A$1:$H$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RMU WAYS'!$A$1:$F$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -185,18 +187,18 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -586,7 +588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B40"/>
+  <dimension ref="B1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -603,7 +605,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Fill in PARENT_ID and SPUR_ID. Everything else is already populated from 'DTC DETAILS U4.xlsx'.</t>
+          <t>Fill in PARENT_ID, SPUR_ID and WAY. Everything else is already populated from 'DTC DETAILS U4.xlsx'.</t>
         </is>
       </c>
     </row>
@@ -631,7 +633,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>2.  THE FIVE RULES</t>
+          <t>2.  THE SIX RULES</t>
         </is>
       </c>
     </row>
@@ -670,149 +672,177 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="B15" s="3" t="inlineStr">
+    <row r="14" ht="28" customHeight="1">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>6.  WAY is only used when the parent is an RMU. An RMU is a five-way unit - ODin, ODout, VL1, VL2, VL3 - so a child of an RMU must say which way it leaves by. Leave WAY blank everywhere else.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>3.  SHEETS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>NODES    The only mandatory sheet. One row per MUSS, RMU, GOS, pole, DTC and HT service. PARENT_ID is the connection; everything else describes the node.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>SPURS    Auto-generated register of the laterals found in NODES. Rename them here (e.g. 'Kote Road lateral'); the names are for the drawing, not for the tree.</t>
+          <t>NODES    The only mandatory sheet. One row per MUSS, RMU, GOS, pole, DTC and HT service. PARENT_ID is the connection; everything else describes the node.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="B18" s="4" t="inlineStr">
         <is>
+          <t>SPURS    Auto-generated register of the laterals found in NODES. Rename them here (e.g. 'Kote Road lateral'); the names are for the drawing, not for the tree.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>RMU WAYS One row per way of every RMU, five per unit: ODin, ODout, VL1, VL2, VL3. Records the normal state and the label of each way. Prefilled from the RMU rows in NODES; it describes the switchgear, it does not carry the connections.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
           <t>BENDS    Optional. Add rows only where a span has to bend round a block instead of running straight from parent to child. SEQ orders the bend points along that one span.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="B19" s="4" t="inlineStr">
+    <row r="21" ht="28" customHeight="1">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>EXAMPLE  A small, complete feeder showing exactly how the rows should read. Copy its pattern; do not edit it.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="B20" s="4" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>LISTS    Dropdown values. Leave hidden.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="B22" s="3" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>4.  WHAT IS ALREADY FILLED IN</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="B23" s="4" t="inlineStr">
+    <row r="25" ht="15" customHeight="1">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>•  119 DTCs, 5 HT services, 2 MUSS and 2 RMU rows, with the coordinates the master holds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>•  PARENT_ID is pre-filled from a minimum spanning tree and marked BASIS = INFERRED. Treat it as a first draft to correct, never as surveyed fact.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>•  Rows with BASIS = UNKNOWN have no usable GPS or are HT/RMU nodes whose tap is not in the workbook. They need a manual parent.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="B26" s="4" t="inlineStr">
         <is>
+          <t>•  PARENT_ID is pre-filled from a minimum spanning tree and marked BASIS = INFERRED. Treat it as a first draft to correct, never as surveyed fact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>•  Rows with BASIS = UNKNOWN have no usable GPS or are HT/RMU nodes whose tap is not in the workbook. They need a manual parent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="B28" s="4" t="inlineStr">
+        <is>
           <t>•  SPUR_ID is also inferred: the longest path from the MUSS is called T, every branch off it is numbered S1, S2, ...</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="B28" s="3" t="inlineStr">
+    <row r="29" ht="28" customHeight="1">
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>•  RMU WAYS already lists all 10 ways of the 2 RMUs, normally closed. Change a way to NO only if it really sits open.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>5.  COLOURS</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="B29" s="4" t="inlineStr">
+    <row r="32" ht="15" customHeight="1">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Amber BASIS      the parent is inferred - check it</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="B30" s="4" t="inlineStr">
+    <row r="33" ht="15" customHeight="1">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Orange PARENT_ID  no parent yet - the node will be left out of the tree</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="B31" s="4" t="inlineStr">
+    <row r="34" ht="15" customHeight="1">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>Green BASIS      surveyed or read off the existing SLD - trusted</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>6.  WHAT TO DO FIRST</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="56" customHeight="1">
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Start with MRS F1 (the largest feeder). Open the hand-drawn SLD beside this file and, for each DTC, correct PARENT_ID to the pole or DTC it actually hangs from. Add the poles you need as new rows (TYPE = POLE, NODE_ID = P-001 ...). Leave pole coordinates blank if you do not have them - the drawing will place the pole on a straight line between its neighbours, which is good enough for the topology.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="42" customHeight="1">
+    <row r="35" ht="15" customHeight="1">
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>When NODES is complete, the generator can be extended to draw the real trunk and spurs instead of inferring them. This workbook is the collection format; the reader is the next code step. See TOPOLOGY_DATA_REQUIREMENTS.md for the reasoning and the optional extras.</t>
+          <t>Orange WAY       a way is filled in but the node has no parent - it cannot be placed</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="B37" s="3" t="inlineStr">
         <is>
+          <t>6.  WHAT TO DO FIRST</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="56" customHeight="1">
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Start with MRS F1 (the largest feeder). Open the hand-drawn SLD beside this file and, for each DTC, correct PARENT_ID to the pole or DTC it actually hangs from. Add the poles you need as new rows (TYPE = POLE, NODE_ID = P-001 ...). Leave pole coordinates blank if you do not have them - the drawing will place the pole on a straight line between its neighbours, which is good enough for the topology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="42" customHeight="1">
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>When NODES is complete, the generator can be extended to draw the real trunk and spurs instead of inferring them. This workbook is the collection format; the reader is the next code step. See TOPOLOGY_DATA_REQUIREMENTS.md for the reasoning and the optional extras.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="B41" s="3" t="inlineStr">
+        <is>
           <t>7.  REBUILDING THIS TEMPLATE</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="28" customHeight="1">
-      <c r="B38" s="5" t="inlineStr">
+    <row r="42" ht="28" customHeight="1">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>python sld_generator.py --topology-template          # refuses to overwrite a filled file
 python sld_generator.py --topology-template --force  # discards your edits and rebuilds</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="28" customHeight="1">
-      <c r="B40" s="6" t="inlineStr">
+    <row r="44" ht="28" customHeight="1">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>Coordinates are decimal degrees. Valid values for this area: lat about 13.9, long about 75.5. A latitude of 3.9 means a dropped leading digit.</t>
         </is>
@@ -829,7 +859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N129"/>
+  <dimension ref="A1:O129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -840,12 +870,13 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
     <col width="7" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="52" customWidth="1" min="14" max="14"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="52" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -891,30 +922,35 @@
       </c>
       <c r="I1" s="7" t="inlineStr">
         <is>
+          <t>WAY</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
           <t>KVA</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>PHASE</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>NORMALLY</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>CONDUCTOR</t>
         </is>
       </c>
-      <c r="M1" s="7" t="inlineStr">
+      <c r="N1" s="7" t="inlineStr">
         <is>
           <t>BASIS</t>
         </is>
       </c>
-      <c r="N1" s="7" t="inlineStr">
+      <c r="O1" s="7" t="inlineStr">
         <is>
           <t>REMARKS</t>
         </is>
@@ -952,13 +988,14 @@
       <c r="I2" s="9" t="inlineStr"/>
       <c r="J2" s="9" t="inlineStr"/>
       <c r="K2" s="9" t="inlineStr"/>
-      <c r="L2" s="8" t="inlineStr"/>
-      <c r="M2" s="9" t="inlineStr">
+      <c r="L2" s="9" t="inlineStr"/>
+      <c r="M2" s="8" t="inlineStr"/>
+      <c r="N2" s="9" t="inlineStr">
         <is>
           <t>SOURCE</t>
         </is>
       </c>
-      <c r="N2" s="10" t="inlineStr">
+      <c r="O2" s="10" t="inlineStr">
         <is>
           <t>Root - no parent. Feeds: MRS F1</t>
         </is>
@@ -996,19 +1033,20 @@
       <c r="I3" s="13" t="inlineStr"/>
       <c r="J3" s="13" t="inlineStr"/>
       <c r="K3" s="13" t="inlineStr"/>
-      <c r="L3" s="12" t="inlineStr"/>
-      <c r="M3" s="13" t="inlineStr">
+      <c r="L3" s="13" t="inlineStr"/>
+      <c r="M3" s="12" t="inlineStr"/>
+      <c r="N3" s="13" t="inlineStr">
         <is>
           <t>SOURCE</t>
         </is>
       </c>
-      <c r="N3" s="14" t="inlineStr">
+      <c r="O3" s="14" t="inlineStr">
         <is>
           <t>Root - no parent. Feeds: Mandli F22, Mandli F13, Mandli F3</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="27" customHeight="1">
+    <row r="4" ht="51" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>RMU-KOTE-ROAD</t>
@@ -1039,24 +1077,25 @@
       <c r="H4" s="9" t="inlineStr"/>
       <c r="I4" s="9" t="inlineStr"/>
       <c r="J4" s="9" t="inlineStr"/>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="9" t="inlineStr"/>
+      <c r="L4" s="9" t="inlineStr">
         <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="L4" s="8" t="inlineStr"/>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="M4" s="8" t="inlineStr"/>
+      <c r="N4" s="9" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="N4" s="10" t="inlineStr">
-        <is>
-          <t>Set PARENT_ID = incoming way; its children are the other ways</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="27" customHeight="1">
+      <c r="O4" s="10" t="inlineStr">
+        <is>
+          <t>5-way RMU: ODin, ODout, VL1, VL2, VL3. Set PARENT_ID = the node it is fed from (that link is way ODin); each child names its way in WAY. See the RMU WAYS sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="51" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>RMU-GANGOTHTI-COLLEGE</t>
@@ -1087,20 +1126,21 @@
       <c r="H5" s="13" t="inlineStr"/>
       <c r="I5" s="13" t="inlineStr"/>
       <c r="J5" s="13" t="inlineStr"/>
-      <c r="K5" s="13" t="inlineStr">
+      <c r="K5" s="13" t="inlineStr"/>
+      <c r="L5" s="13" t="inlineStr">
         <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="L5" s="12" t="inlineStr"/>
-      <c r="M5" s="13" t="inlineStr">
+      <c r="M5" s="12" t="inlineStr"/>
+      <c r="N5" s="13" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="N5" s="14" t="inlineStr">
-        <is>
-          <t>Set PARENT_ID = incoming way; its children are the other ways</t>
+      <c r="O5" s="14" t="inlineStr">
+        <is>
+          <t>5-way RMU: ODin, ODout, VL1, VL2, VL3. Set PARENT_ID = the node it is fed from (that link is way ODin); each child names its way in WAY. See the RMU WAYS sheet</t>
         </is>
       </c>
     </row>
@@ -1141,18 +1181,19 @@
           <t>S1</t>
         </is>
       </c>
-      <c r="I6" s="9" t="n">
+      <c r="I6" s="9" t="inlineStr"/>
+      <c r="J6" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="J6" s="9" t="inlineStr"/>
       <c r="K6" s="9" t="inlineStr"/>
-      <c r="L6" s="8" t="inlineStr"/>
-      <c r="M6" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N6" s="10" t="inlineStr"/>
+      <c r="L6" s="9" t="inlineStr"/>
+      <c r="M6" s="8" t="inlineStr"/>
+      <c r="N6" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O6" s="10" t="inlineStr"/>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
@@ -1191,18 +1232,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I7" s="13" t="n">
+      <c r="I7" s="13" t="inlineStr"/>
+      <c r="J7" s="13" t="n">
         <v>200</v>
       </c>
-      <c r="J7" s="13" t="inlineStr"/>
       <c r="K7" s="13" t="inlineStr"/>
-      <c r="L7" s="12" t="inlineStr"/>
-      <c r="M7" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N7" s="14" t="inlineStr"/>
+      <c r="L7" s="13" t="inlineStr"/>
+      <c r="M7" s="12" t="inlineStr"/>
+      <c r="N7" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O7" s="14" t="inlineStr"/>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
@@ -1241,18 +1283,19 @@
           <t>S5</t>
         </is>
       </c>
-      <c r="I8" s="9" t="n">
+      <c r="I8" s="9" t="inlineStr"/>
+      <c r="J8" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="J8" s="9" t="inlineStr"/>
       <c r="K8" s="9" t="inlineStr"/>
-      <c r="L8" s="8" t="inlineStr"/>
-      <c r="M8" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N8" s="10" t="inlineStr"/>
+      <c r="L8" s="9" t="inlineStr"/>
+      <c r="M8" s="8" t="inlineStr"/>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O8" s="10" t="inlineStr"/>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
@@ -1291,18 +1334,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I9" s="13" t="n">
+      <c r="I9" s="13" t="inlineStr"/>
+      <c r="J9" s="13" t="n">
         <v>250</v>
       </c>
-      <c r="J9" s="13" t="inlineStr"/>
       <c r="K9" s="13" t="inlineStr"/>
-      <c r="L9" s="12" t="inlineStr"/>
-      <c r="M9" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N9" s="14" t="inlineStr"/>
+      <c r="L9" s="13" t="inlineStr"/>
+      <c r="M9" s="12" t="inlineStr"/>
+      <c r="N9" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O9" s="14" t="inlineStr"/>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
@@ -1341,18 +1385,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I10" s="9" t="n">
+      <c r="I10" s="9" t="inlineStr"/>
+      <c r="J10" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="J10" s="9" t="inlineStr"/>
       <c r="K10" s="9" t="inlineStr"/>
-      <c r="L10" s="8" t="inlineStr"/>
-      <c r="M10" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N10" s="10" t="inlineStr"/>
+      <c r="L10" s="9" t="inlineStr"/>
+      <c r="M10" s="8" t="inlineStr"/>
+      <c r="N10" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O10" s="10" t="inlineStr"/>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
@@ -1391,18 +1436,19 @@
           <t>S1</t>
         </is>
       </c>
-      <c r="I11" s="13" t="n">
+      <c r="I11" s="13" t="inlineStr"/>
+      <c r="J11" s="13" t="n">
         <v>250</v>
       </c>
-      <c r="J11" s="13" t="inlineStr"/>
       <c r="K11" s="13" t="inlineStr"/>
-      <c r="L11" s="12" t="inlineStr"/>
-      <c r="M11" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N11" s="14" t="inlineStr"/>
+      <c r="L11" s="13" t="inlineStr"/>
+      <c r="M11" s="12" t="inlineStr"/>
+      <c r="N11" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O11" s="14" t="inlineStr"/>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
@@ -1441,18 +1487,19 @@
           <t>S2</t>
         </is>
       </c>
-      <c r="I12" s="9" t="n">
+      <c r="I12" s="9" t="inlineStr"/>
+      <c r="J12" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="J12" s="9" t="inlineStr"/>
       <c r="K12" s="9" t="inlineStr"/>
-      <c r="L12" s="8" t="inlineStr"/>
-      <c r="M12" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N12" s="10" t="inlineStr"/>
+      <c r="L12" s="9" t="inlineStr"/>
+      <c r="M12" s="8" t="inlineStr"/>
+      <c r="N12" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O12" s="10" t="inlineStr"/>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
@@ -1491,18 +1538,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I13" s="13" t="n">
+      <c r="I13" s="13" t="inlineStr"/>
+      <c r="J13" s="13" t="n">
         <v>250</v>
       </c>
-      <c r="J13" s="13" t="inlineStr"/>
       <c r="K13" s="13" t="inlineStr"/>
-      <c r="L13" s="12" t="inlineStr"/>
-      <c r="M13" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N13" s="14" t="inlineStr"/>
+      <c r="L13" s="13" t="inlineStr"/>
+      <c r="M13" s="12" t="inlineStr"/>
+      <c r="N13" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O13" s="14" t="inlineStr"/>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
@@ -1541,18 +1589,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I14" s="9" t="n">
+      <c r="I14" s="9" t="inlineStr"/>
+      <c r="J14" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="J14" s="9" t="inlineStr"/>
       <c r="K14" s="9" t="inlineStr"/>
-      <c r="L14" s="8" t="inlineStr"/>
-      <c r="M14" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N14" s="10" t="inlineStr"/>
+      <c r="L14" s="9" t="inlineStr"/>
+      <c r="M14" s="8" t="inlineStr"/>
+      <c r="N14" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O14" s="10" t="inlineStr"/>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
@@ -1591,18 +1640,19 @@
           <t>S3</t>
         </is>
       </c>
-      <c r="I15" s="13" t="n">
+      <c r="I15" s="13" t="inlineStr"/>
+      <c r="J15" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="J15" s="13" t="inlineStr"/>
       <c r="K15" s="13" t="inlineStr"/>
-      <c r="L15" s="12" t="inlineStr"/>
-      <c r="M15" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N15" s="14" t="inlineStr"/>
+      <c r="L15" s="13" t="inlineStr"/>
+      <c r="M15" s="12" t="inlineStr"/>
+      <c r="N15" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O15" s="14" t="inlineStr"/>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
@@ -1641,18 +1691,19 @@
           <t>S5</t>
         </is>
       </c>
-      <c r="I16" s="9" t="n">
+      <c r="I16" s="9" t="inlineStr"/>
+      <c r="J16" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="J16" s="9" t="inlineStr"/>
       <c r="K16" s="9" t="inlineStr"/>
-      <c r="L16" s="8" t="inlineStr"/>
-      <c r="M16" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N16" s="10" t="inlineStr"/>
+      <c r="L16" s="9" t="inlineStr"/>
+      <c r="M16" s="8" t="inlineStr"/>
+      <c r="N16" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O16" s="10" t="inlineStr"/>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
@@ -1691,18 +1742,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I17" s="13" t="n">
+      <c r="I17" s="13" t="inlineStr"/>
+      <c r="J17" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="J17" s="13" t="inlineStr"/>
       <c r="K17" s="13" t="inlineStr"/>
-      <c r="L17" s="12" t="inlineStr"/>
-      <c r="M17" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N17" s="14" t="inlineStr"/>
+      <c r="L17" s="13" t="inlineStr"/>
+      <c r="M17" s="12" t="inlineStr"/>
+      <c r="N17" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O17" s="14" t="inlineStr"/>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
@@ -1741,18 +1793,19 @@
           <t>S9</t>
         </is>
       </c>
-      <c r="I18" s="9" t="n">
+      <c r="I18" s="9" t="inlineStr"/>
+      <c r="J18" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="J18" s="9" t="inlineStr"/>
       <c r="K18" s="9" t="inlineStr"/>
-      <c r="L18" s="8" t="inlineStr"/>
-      <c r="M18" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N18" s="10" t="inlineStr"/>
+      <c r="L18" s="9" t="inlineStr"/>
+      <c r="M18" s="8" t="inlineStr"/>
+      <c r="N18" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O18" s="10" t="inlineStr"/>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
@@ -1791,18 +1844,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I19" s="13" t="n">
+      <c r="I19" s="13" t="inlineStr"/>
+      <c r="J19" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="J19" s="13" t="inlineStr"/>
       <c r="K19" s="13" t="inlineStr"/>
-      <c r="L19" s="12" t="inlineStr"/>
-      <c r="M19" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N19" s="14" t="inlineStr"/>
+      <c r="L19" s="13" t="inlineStr"/>
+      <c r="M19" s="12" t="inlineStr"/>
+      <c r="N19" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O19" s="14" t="inlineStr"/>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
@@ -1841,18 +1895,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I20" s="9" t="n">
+      <c r="I20" s="9" t="inlineStr"/>
+      <c r="J20" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="J20" s="9" t="inlineStr"/>
       <c r="K20" s="9" t="inlineStr"/>
-      <c r="L20" s="8" t="inlineStr"/>
-      <c r="M20" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N20" s="10" t="inlineStr"/>
+      <c r="L20" s="9" t="inlineStr"/>
+      <c r="M20" s="8" t="inlineStr"/>
+      <c r="N20" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O20" s="10" t="inlineStr"/>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="12" t="inlineStr">
@@ -1891,18 +1946,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I21" s="13" t="n">
+      <c r="I21" s="13" t="inlineStr"/>
+      <c r="J21" s="13" t="n">
         <v>250</v>
       </c>
-      <c r="J21" s="13" t="inlineStr"/>
       <c r="K21" s="13" t="inlineStr"/>
-      <c r="L21" s="12" t="inlineStr"/>
-      <c r="M21" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N21" s="14" t="inlineStr"/>
+      <c r="L21" s="13" t="inlineStr"/>
+      <c r="M21" s="12" t="inlineStr"/>
+      <c r="N21" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O21" s="14" t="inlineStr"/>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
@@ -1941,18 +1997,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I22" s="9" t="n">
+      <c r="I22" s="9" t="inlineStr"/>
+      <c r="J22" s="9" t="n">
         <v>63</v>
       </c>
-      <c r="J22" s="9" t="inlineStr"/>
       <c r="K22" s="9" t="inlineStr"/>
-      <c r="L22" s="8" t="inlineStr"/>
-      <c r="M22" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N22" s="10" t="inlineStr"/>
+      <c r="L22" s="9" t="inlineStr"/>
+      <c r="M22" s="8" t="inlineStr"/>
+      <c r="N22" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O22" s="10" t="inlineStr"/>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="12" t="inlineStr">
@@ -1991,18 +2048,19 @@
           <t>S5</t>
         </is>
       </c>
-      <c r="I23" s="13" t="n">
+      <c r="I23" s="13" t="inlineStr"/>
+      <c r="J23" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="J23" s="13" t="inlineStr"/>
       <c r="K23" s="13" t="inlineStr"/>
-      <c r="L23" s="12" t="inlineStr"/>
-      <c r="M23" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N23" s="14" t="inlineStr"/>
+      <c r="L23" s="13" t="inlineStr"/>
+      <c r="M23" s="12" t="inlineStr"/>
+      <c r="N23" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O23" s="14" t="inlineStr"/>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
@@ -2041,18 +2099,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I24" s="9" t="n">
+      <c r="I24" s="9" t="inlineStr"/>
+      <c r="J24" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="J24" s="9" t="inlineStr"/>
       <c r="K24" s="9" t="inlineStr"/>
-      <c r="L24" s="8" t="inlineStr"/>
-      <c r="M24" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N24" s="10" t="inlineStr"/>
+      <c r="L24" s="9" t="inlineStr"/>
+      <c r="M24" s="8" t="inlineStr"/>
+      <c r="N24" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O24" s="10" t="inlineStr"/>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="12" t="inlineStr">
@@ -2091,18 +2150,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I25" s="13" t="n">
+      <c r="I25" s="13" t="inlineStr"/>
+      <c r="J25" s="13" t="n">
         <v>63</v>
       </c>
-      <c r="J25" s="13" t="inlineStr"/>
       <c r="K25" s="13" t="inlineStr"/>
-      <c r="L25" s="12" t="inlineStr"/>
-      <c r="M25" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N25" s="14" t="inlineStr"/>
+      <c r="L25" s="13" t="inlineStr"/>
+      <c r="M25" s="12" t="inlineStr"/>
+      <c r="N25" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O25" s="14" t="inlineStr"/>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
@@ -2141,18 +2201,19 @@
           <t>S1</t>
         </is>
       </c>
-      <c r="I26" s="9" t="n">
+      <c r="I26" s="9" t="inlineStr"/>
+      <c r="J26" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="J26" s="9" t="inlineStr"/>
       <c r="K26" s="9" t="inlineStr"/>
-      <c r="L26" s="8" t="inlineStr"/>
-      <c r="M26" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N26" s="10" t="inlineStr"/>
+      <c r="L26" s="9" t="inlineStr"/>
+      <c r="M26" s="8" t="inlineStr"/>
+      <c r="N26" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O26" s="10" t="inlineStr"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="12" t="inlineStr">
@@ -2191,18 +2252,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I27" s="13" t="n">
+      <c r="I27" s="13" t="inlineStr"/>
+      <c r="J27" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="J27" s="13" t="inlineStr"/>
       <c r="K27" s="13" t="inlineStr"/>
-      <c r="L27" s="12" t="inlineStr"/>
-      <c r="M27" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N27" s="14" t="inlineStr"/>
+      <c r="L27" s="13" t="inlineStr"/>
+      <c r="M27" s="12" t="inlineStr"/>
+      <c r="N27" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O27" s="14" t="inlineStr"/>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
@@ -2241,18 +2303,19 @@
           <t>S2</t>
         </is>
       </c>
-      <c r="I28" s="9" t="n">
+      <c r="I28" s="9" t="inlineStr"/>
+      <c r="J28" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="J28" s="9" t="inlineStr"/>
       <c r="K28" s="9" t="inlineStr"/>
-      <c r="L28" s="8" t="inlineStr"/>
-      <c r="M28" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N28" s="10" t="inlineStr"/>
+      <c r="L28" s="9" t="inlineStr"/>
+      <c r="M28" s="8" t="inlineStr"/>
+      <c r="N28" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O28" s="10" t="inlineStr"/>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="12" t="inlineStr">
@@ -2291,18 +2354,19 @@
           <t>S6</t>
         </is>
       </c>
-      <c r="I29" s="13" t="n">
+      <c r="I29" s="13" t="inlineStr"/>
+      <c r="J29" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="J29" s="13" t="inlineStr"/>
       <c r="K29" s="13" t="inlineStr"/>
-      <c r="L29" s="12" t="inlineStr"/>
-      <c r="M29" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N29" s="14" t="inlineStr"/>
+      <c r="L29" s="13" t="inlineStr"/>
+      <c r="M29" s="12" t="inlineStr"/>
+      <c r="N29" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O29" s="14" t="inlineStr"/>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
@@ -2341,18 +2405,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I30" s="9" t="n">
+      <c r="I30" s="9" t="inlineStr"/>
+      <c r="J30" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="J30" s="9" t="inlineStr"/>
       <c r="K30" s="9" t="inlineStr"/>
-      <c r="L30" s="8" t="inlineStr"/>
-      <c r="M30" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N30" s="10" t="inlineStr"/>
+      <c r="L30" s="9" t="inlineStr"/>
+      <c r="M30" s="8" t="inlineStr"/>
+      <c r="N30" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O30" s="10" t="inlineStr"/>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="12" t="inlineStr">
@@ -2391,18 +2456,19 @@
           <t>S11</t>
         </is>
       </c>
-      <c r="I31" s="13" t="n">
+      <c r="I31" s="13" t="inlineStr"/>
+      <c r="J31" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="J31" s="13" t="inlineStr"/>
       <c r="K31" s="13" t="inlineStr"/>
-      <c r="L31" s="12" t="inlineStr"/>
-      <c r="M31" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N31" s="14" t="inlineStr">
+      <c r="L31" s="13" t="inlineStr"/>
+      <c r="M31" s="12" t="inlineStr"/>
+      <c r="N31" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O31" s="14" t="inlineStr">
         <is>
           <t>shared coordinate with SCD-106</t>
         </is>
@@ -2445,18 +2511,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I32" s="9" t="n">
+      <c r="I32" s="9" t="inlineStr"/>
+      <c r="J32" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="J32" s="9" t="inlineStr"/>
       <c r="K32" s="9" t="inlineStr"/>
-      <c r="L32" s="8" t="inlineStr"/>
-      <c r="M32" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N32" s="10" t="inlineStr"/>
+      <c r="L32" s="9" t="inlineStr"/>
+      <c r="M32" s="8" t="inlineStr"/>
+      <c r="N32" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O32" s="10" t="inlineStr"/>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="12" t="inlineStr">
@@ -2495,18 +2562,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I33" s="13" t="n">
+      <c r="I33" s="13" t="inlineStr"/>
+      <c r="J33" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="J33" s="13" t="inlineStr"/>
       <c r="K33" s="13" t="inlineStr"/>
-      <c r="L33" s="12" t="inlineStr"/>
-      <c r="M33" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N33" s="14" t="inlineStr"/>
+      <c r="L33" s="13" t="inlineStr"/>
+      <c r="M33" s="12" t="inlineStr"/>
+      <c r="N33" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O33" s="14" t="inlineStr"/>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
@@ -2545,18 +2613,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I34" s="9" t="n">
+      <c r="I34" s="9" t="inlineStr"/>
+      <c r="J34" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="J34" s="9" t="inlineStr"/>
       <c r="K34" s="9" t="inlineStr"/>
-      <c r="L34" s="8" t="inlineStr"/>
-      <c r="M34" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N34" s="10" t="inlineStr"/>
+      <c r="L34" s="9" t="inlineStr"/>
+      <c r="M34" s="8" t="inlineStr"/>
+      <c r="N34" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O34" s="10" t="inlineStr"/>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="12" t="inlineStr">
@@ -2595,18 +2664,19 @@
           <t>S7</t>
         </is>
       </c>
-      <c r="I35" s="13" t="n">
+      <c r="I35" s="13" t="inlineStr"/>
+      <c r="J35" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="J35" s="13" t="inlineStr"/>
       <c r="K35" s="13" t="inlineStr"/>
-      <c r="L35" s="12" t="inlineStr"/>
-      <c r="M35" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N35" s="14" t="inlineStr"/>
+      <c r="L35" s="13" t="inlineStr"/>
+      <c r="M35" s="12" t="inlineStr"/>
+      <c r="N35" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O35" s="14" t="inlineStr"/>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
@@ -2645,18 +2715,19 @@
           <t>S1</t>
         </is>
       </c>
-      <c r="I36" s="9" t="n">
+      <c r="I36" s="9" t="inlineStr"/>
+      <c r="J36" s="9" t="n">
         <v>63</v>
       </c>
-      <c r="J36" s="9" t="inlineStr"/>
       <c r="K36" s="9" t="inlineStr"/>
-      <c r="L36" s="8" t="inlineStr"/>
-      <c r="M36" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N36" s="10" t="inlineStr"/>
+      <c r="L36" s="9" t="inlineStr"/>
+      <c r="M36" s="8" t="inlineStr"/>
+      <c r="N36" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O36" s="10" t="inlineStr"/>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" s="12" t="inlineStr">
@@ -2695,18 +2766,19 @@
           <t>S5</t>
         </is>
       </c>
-      <c r="I37" s="13" t="n">
+      <c r="I37" s="13" t="inlineStr"/>
+      <c r="J37" s="13" t="n">
         <v>63</v>
       </c>
-      <c r="J37" s="13" t="inlineStr"/>
       <c r="K37" s="13" t="inlineStr"/>
-      <c r="L37" s="12" t="inlineStr"/>
-      <c r="M37" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N37" s="14" t="inlineStr"/>
+      <c r="L37" s="13" t="inlineStr"/>
+      <c r="M37" s="12" t="inlineStr"/>
+      <c r="N37" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O37" s="14" t="inlineStr"/>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
@@ -2745,18 +2817,19 @@
           <t>S8</t>
         </is>
       </c>
-      <c r="I38" s="9" t="n">
+      <c r="I38" s="9" t="inlineStr"/>
+      <c r="J38" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="J38" s="9" t="inlineStr"/>
       <c r="K38" s="9" t="inlineStr"/>
-      <c r="L38" s="8" t="inlineStr"/>
-      <c r="M38" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N38" s="10" t="inlineStr"/>
+      <c r="L38" s="9" t="inlineStr"/>
+      <c r="M38" s="8" t="inlineStr"/>
+      <c r="N38" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O38" s="10" t="inlineStr"/>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" s="12" t="inlineStr">
@@ -2795,18 +2868,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I39" s="13" t="n">
+      <c r="I39" s="13" t="inlineStr"/>
+      <c r="J39" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="J39" s="13" t="inlineStr"/>
       <c r="K39" s="13" t="inlineStr"/>
-      <c r="L39" s="12" t="inlineStr"/>
-      <c r="M39" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N39" s="14" t="inlineStr"/>
+      <c r="L39" s="13" t="inlineStr"/>
+      <c r="M39" s="12" t="inlineStr"/>
+      <c r="N39" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O39" s="14" t="inlineStr"/>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
@@ -2845,18 +2919,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I40" s="9" t="n">
+      <c r="I40" s="9" t="inlineStr"/>
+      <c r="J40" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="J40" s="9" t="inlineStr"/>
       <c r="K40" s="9" t="inlineStr"/>
-      <c r="L40" s="8" t="inlineStr"/>
-      <c r="M40" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N40" s="10" t="inlineStr"/>
+      <c r="L40" s="9" t="inlineStr"/>
+      <c r="M40" s="8" t="inlineStr"/>
+      <c r="N40" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O40" s="10" t="inlineStr"/>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" s="12" t="inlineStr">
@@ -2887,18 +2962,19 @@
       </c>
       <c r="G41" s="12" t="inlineStr"/>
       <c r="H41" s="13" t="inlineStr"/>
-      <c r="I41" s="13" t="n">
+      <c r="I41" s="13" t="inlineStr"/>
+      <c r="J41" s="13" t="n">
         <v>63</v>
       </c>
-      <c r="J41" s="13" t="inlineStr"/>
       <c r="K41" s="13" t="inlineStr"/>
-      <c r="L41" s="12" t="inlineStr"/>
-      <c r="M41" s="13" t="inlineStr">
+      <c r="L41" s="13" t="inlineStr"/>
+      <c r="M41" s="12" t="inlineStr"/>
+      <c r="N41" s="13" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="N41" s="14" t="inlineStr">
+      <c r="O41" s="14" t="inlineStr">
         <is>
           <t>no usable GPS - set PARENT_ID by hand</t>
         </is>
@@ -2941,18 +3017,19 @@
           <t>S5</t>
         </is>
       </c>
-      <c r="I42" s="9" t="n">
+      <c r="I42" s="9" t="inlineStr"/>
+      <c r="J42" s="9" t="n">
         <v>63</v>
       </c>
-      <c r="J42" s="9" t="inlineStr"/>
       <c r="K42" s="9" t="inlineStr"/>
-      <c r="L42" s="8" t="inlineStr"/>
-      <c r="M42" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N42" s="10" t="inlineStr"/>
+      <c r="L42" s="9" t="inlineStr"/>
+      <c r="M42" s="8" t="inlineStr"/>
+      <c r="N42" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O42" s="10" t="inlineStr"/>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" s="12" t="inlineStr">
@@ -2991,18 +3068,19 @@
           <t>S9</t>
         </is>
       </c>
-      <c r="I43" s="13" t="n">
+      <c r="I43" s="13" t="inlineStr"/>
+      <c r="J43" s="13" t="n">
         <v>63</v>
       </c>
-      <c r="J43" s="13" t="inlineStr"/>
       <c r="K43" s="13" t="inlineStr"/>
-      <c r="L43" s="12" t="inlineStr"/>
-      <c r="M43" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N43" s="14" t="inlineStr"/>
+      <c r="L43" s="13" t="inlineStr"/>
+      <c r="M43" s="12" t="inlineStr"/>
+      <c r="N43" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O43" s="14" t="inlineStr"/>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" s="8" t="inlineStr">
@@ -3041,18 +3119,19 @@
           <t>S2</t>
         </is>
       </c>
-      <c r="I44" s="9" t="n">
+      <c r="I44" s="9" t="inlineStr"/>
+      <c r="J44" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="J44" s="9" t="inlineStr"/>
       <c r="K44" s="9" t="inlineStr"/>
-      <c r="L44" s="8" t="inlineStr"/>
-      <c r="M44" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N44" s="10" t="inlineStr"/>
+      <c r="L44" s="9" t="inlineStr"/>
+      <c r="M44" s="8" t="inlineStr"/>
+      <c r="N44" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O44" s="10" t="inlineStr"/>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" s="12" t="inlineStr">
@@ -3091,18 +3170,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I45" s="13" t="n">
+      <c r="I45" s="13" t="inlineStr"/>
+      <c r="J45" s="13" t="n">
         <v>63</v>
       </c>
-      <c r="J45" s="13" t="inlineStr"/>
       <c r="K45" s="13" t="inlineStr"/>
-      <c r="L45" s="12" t="inlineStr"/>
-      <c r="M45" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N45" s="14" t="inlineStr"/>
+      <c r="L45" s="13" t="inlineStr"/>
+      <c r="M45" s="12" t="inlineStr"/>
+      <c r="N45" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O45" s="14" t="inlineStr"/>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" s="8" t="inlineStr">
@@ -3141,18 +3221,19 @@
           <t>S10</t>
         </is>
       </c>
-      <c r="I46" s="9" t="n">
+      <c r="I46" s="9" t="inlineStr"/>
+      <c r="J46" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="J46" s="9" t="inlineStr"/>
       <c r="K46" s="9" t="inlineStr"/>
-      <c r="L46" s="8" t="inlineStr"/>
-      <c r="M46" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N46" s="10" t="inlineStr"/>
+      <c r="L46" s="9" t="inlineStr"/>
+      <c r="M46" s="8" t="inlineStr"/>
+      <c r="N46" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O46" s="10" t="inlineStr"/>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" s="12" t="inlineStr">
@@ -3191,18 +3272,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I47" s="13" t="n">
+      <c r="I47" s="13" t="inlineStr"/>
+      <c r="J47" s="13" t="n">
         <v>63</v>
       </c>
-      <c r="J47" s="13" t="inlineStr"/>
       <c r="K47" s="13" t="inlineStr"/>
-      <c r="L47" s="12" t="inlineStr"/>
-      <c r="M47" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N47" s="14" t="inlineStr"/>
+      <c r="L47" s="13" t="inlineStr"/>
+      <c r="M47" s="12" t="inlineStr"/>
+      <c r="N47" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O47" s="14" t="inlineStr"/>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" s="8" t="inlineStr">
@@ -3241,18 +3323,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I48" s="9" t="n">
+      <c r="I48" s="9" t="inlineStr"/>
+      <c r="J48" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="J48" s="9" t="inlineStr"/>
       <c r="K48" s="9" t="inlineStr"/>
-      <c r="L48" s="8" t="inlineStr"/>
-      <c r="M48" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N48" s="10" t="inlineStr"/>
+      <c r="L48" s="9" t="inlineStr"/>
+      <c r="M48" s="8" t="inlineStr"/>
+      <c r="N48" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O48" s="10" t="inlineStr"/>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" s="12" t="inlineStr">
@@ -3291,18 +3374,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I49" s="13" t="n">
+      <c r="I49" s="13" t="inlineStr"/>
+      <c r="J49" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="J49" s="13" t="inlineStr"/>
       <c r="K49" s="13" t="inlineStr"/>
-      <c r="L49" s="12" t="inlineStr"/>
-      <c r="M49" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N49" s="14" t="inlineStr"/>
+      <c r="L49" s="13" t="inlineStr"/>
+      <c r="M49" s="12" t="inlineStr"/>
+      <c r="N49" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O49" s="14" t="inlineStr"/>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" s="8" t="inlineStr">
@@ -3341,18 +3425,19 @@
           <t>S5</t>
         </is>
       </c>
-      <c r="I50" s="9" t="n">
+      <c r="I50" s="9" t="inlineStr"/>
+      <c r="J50" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="J50" s="9" t="inlineStr"/>
       <c r="K50" s="9" t="inlineStr"/>
-      <c r="L50" s="8" t="inlineStr"/>
-      <c r="M50" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N50" s="10" t="inlineStr"/>
+      <c r="L50" s="9" t="inlineStr"/>
+      <c r="M50" s="8" t="inlineStr"/>
+      <c r="N50" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O50" s="10" t="inlineStr"/>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" s="12" t="inlineStr">
@@ -3391,18 +3476,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I51" s="13" t="n">
+      <c r="I51" s="13" t="inlineStr"/>
+      <c r="J51" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="J51" s="13" t="inlineStr"/>
       <c r="K51" s="13" t="inlineStr"/>
-      <c r="L51" s="12" t="inlineStr"/>
-      <c r="M51" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N51" s="14" t="inlineStr"/>
+      <c r="L51" s="13" t="inlineStr"/>
+      <c r="M51" s="12" t="inlineStr"/>
+      <c r="N51" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O51" s="14" t="inlineStr"/>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" s="8" t="inlineStr">
@@ -3441,18 +3527,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I52" s="9" t="n">
+      <c r="I52" s="9" t="inlineStr"/>
+      <c r="J52" s="9" t="n">
         <v>63</v>
       </c>
-      <c r="J52" s="9" t="inlineStr"/>
       <c r="K52" s="9" t="inlineStr"/>
-      <c r="L52" s="8" t="inlineStr"/>
-      <c r="M52" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N52" s="10" t="inlineStr"/>
+      <c r="L52" s="9" t="inlineStr"/>
+      <c r="M52" s="8" t="inlineStr"/>
+      <c r="N52" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O52" s="10" t="inlineStr"/>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" s="12" t="inlineStr">
@@ -3491,18 +3578,19 @@
           <t>S5</t>
         </is>
       </c>
-      <c r="I53" s="13" t="n">
+      <c r="I53" s="13" t="inlineStr"/>
+      <c r="J53" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="J53" s="13" t="inlineStr"/>
       <c r="K53" s="13" t="inlineStr"/>
-      <c r="L53" s="12" t="inlineStr"/>
-      <c r="M53" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N53" s="14" t="inlineStr"/>
+      <c r="L53" s="13" t="inlineStr"/>
+      <c r="M53" s="12" t="inlineStr"/>
+      <c r="N53" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O53" s="14" t="inlineStr"/>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" s="8" t="inlineStr">
@@ -3541,18 +3629,19 @@
           <t>S1</t>
         </is>
       </c>
-      <c r="I54" s="9" t="n">
+      <c r="I54" s="9" t="inlineStr"/>
+      <c r="J54" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="J54" s="9" t="inlineStr"/>
       <c r="K54" s="9" t="inlineStr"/>
-      <c r="L54" s="8" t="inlineStr"/>
-      <c r="M54" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N54" s="10" t="inlineStr"/>
+      <c r="L54" s="9" t="inlineStr"/>
+      <c r="M54" s="8" t="inlineStr"/>
+      <c r="N54" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O54" s="10" t="inlineStr"/>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" s="12" t="inlineStr">
@@ -3591,18 +3680,19 @@
           <t>S12</t>
         </is>
       </c>
-      <c r="I55" s="13" t="n">
+      <c r="I55" s="13" t="inlineStr"/>
+      <c r="J55" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="J55" s="13" t="inlineStr"/>
       <c r="K55" s="13" t="inlineStr"/>
-      <c r="L55" s="12" t="inlineStr"/>
-      <c r="M55" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N55" s="14" t="inlineStr"/>
+      <c r="L55" s="13" t="inlineStr"/>
+      <c r="M55" s="12" t="inlineStr"/>
+      <c r="N55" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O55" s="14" t="inlineStr"/>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="8" t="inlineStr">
@@ -3641,18 +3731,19 @@
           <t>S5</t>
         </is>
       </c>
-      <c r="I56" s="9" t="n">
+      <c r="I56" s="9" t="inlineStr"/>
+      <c r="J56" s="9" t="n">
         <v>63</v>
       </c>
-      <c r="J56" s="9" t="inlineStr"/>
       <c r="K56" s="9" t="inlineStr"/>
-      <c r="L56" s="8" t="inlineStr"/>
-      <c r="M56" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N56" s="10" t="inlineStr"/>
+      <c r="L56" s="9" t="inlineStr"/>
+      <c r="M56" s="8" t="inlineStr"/>
+      <c r="N56" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O56" s="10" t="inlineStr"/>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" s="12" t="inlineStr">
@@ -3691,18 +3782,19 @@
           <t>S1</t>
         </is>
       </c>
-      <c r="I57" s="13" t="n">
+      <c r="I57" s="13" t="inlineStr"/>
+      <c r="J57" s="13" t="n">
         <v>63</v>
       </c>
-      <c r="J57" s="13" t="inlineStr"/>
       <c r="K57" s="13" t="inlineStr"/>
-      <c r="L57" s="12" t="inlineStr"/>
-      <c r="M57" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N57" s="14" t="inlineStr"/>
+      <c r="L57" s="13" t="inlineStr"/>
+      <c r="M57" s="12" t="inlineStr"/>
+      <c r="N57" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O57" s="14" t="inlineStr"/>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" s="8" t="inlineStr">
@@ -3741,18 +3833,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I58" s="9" t="n">
+      <c r="I58" s="9" t="inlineStr"/>
+      <c r="J58" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="J58" s="9" t="inlineStr"/>
       <c r="K58" s="9" t="inlineStr"/>
-      <c r="L58" s="8" t="inlineStr"/>
-      <c r="M58" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N58" s="10" t="inlineStr"/>
+      <c r="L58" s="9" t="inlineStr"/>
+      <c r="M58" s="8" t="inlineStr"/>
+      <c r="N58" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O58" s="10" t="inlineStr"/>
     </row>
     <row r="59" ht="27" customHeight="1">
       <c r="A59" s="12" t="inlineStr">
@@ -3791,18 +3884,19 @@
           <t>S5</t>
         </is>
       </c>
-      <c r="I59" s="13" t="n">
+      <c r="I59" s="13" t="inlineStr"/>
+      <c r="J59" s="13" t="n">
         <v>63</v>
       </c>
-      <c r="J59" s="13" t="inlineStr"/>
       <c r="K59" s="13" t="inlineStr"/>
-      <c r="L59" s="12" t="inlineStr"/>
-      <c r="M59" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N59" s="14" t="inlineStr"/>
+      <c r="L59" s="13" t="inlineStr"/>
+      <c r="M59" s="12" t="inlineStr"/>
+      <c r="N59" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O59" s="14" t="inlineStr"/>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" s="8" t="inlineStr">
@@ -3841,18 +3935,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I60" s="9" t="n">
+      <c r="I60" s="9" t="inlineStr"/>
+      <c r="J60" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="J60" s="9" t="inlineStr"/>
       <c r="K60" s="9" t="inlineStr"/>
-      <c r="L60" s="8" t="inlineStr"/>
-      <c r="M60" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N60" s="10" t="inlineStr"/>
+      <c r="L60" s="9" t="inlineStr"/>
+      <c r="M60" s="8" t="inlineStr"/>
+      <c r="N60" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O60" s="10" t="inlineStr"/>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="12" t="inlineStr">
@@ -3891,18 +3986,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I61" s="13" t="n">
+      <c r="I61" s="13" t="inlineStr"/>
+      <c r="J61" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="J61" s="13" t="inlineStr"/>
       <c r="K61" s="13" t="inlineStr"/>
-      <c r="L61" s="12" t="inlineStr"/>
-      <c r="M61" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N61" s="14" t="inlineStr"/>
+      <c r="L61" s="13" t="inlineStr"/>
+      <c r="M61" s="12" t="inlineStr"/>
+      <c r="N61" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O61" s="14" t="inlineStr"/>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" s="8" t="inlineStr">
@@ -3941,18 +4037,19 @@
           <t>S8</t>
         </is>
       </c>
-      <c r="I62" s="9" t="n">
+      <c r="I62" s="9" t="inlineStr"/>
+      <c r="J62" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="J62" s="9" t="inlineStr"/>
       <c r="K62" s="9" t="inlineStr"/>
-      <c r="L62" s="8" t="inlineStr"/>
-      <c r="M62" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N62" s="10" t="inlineStr"/>
+      <c r="L62" s="9" t="inlineStr"/>
+      <c r="M62" s="8" t="inlineStr"/>
+      <c r="N62" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O62" s="10" t="inlineStr"/>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" s="12" t="inlineStr">
@@ -3991,18 +4088,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I63" s="13" t="n">
+      <c r="I63" s="13" t="inlineStr"/>
+      <c r="J63" s="13" t="n">
         <v>63</v>
       </c>
-      <c r="J63" s="13" t="inlineStr"/>
       <c r="K63" s="13" t="inlineStr"/>
-      <c r="L63" s="12" t="inlineStr"/>
-      <c r="M63" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N63" s="14" t="inlineStr"/>
+      <c r="L63" s="13" t="inlineStr"/>
+      <c r="M63" s="12" t="inlineStr"/>
+      <c r="N63" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O63" s="14" t="inlineStr"/>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" s="8" t="inlineStr">
@@ -4041,18 +4139,19 @@
           <t>S4</t>
         </is>
       </c>
-      <c r="I64" s="9" t="n">
+      <c r="I64" s="9" t="inlineStr"/>
+      <c r="J64" s="9" t="n">
         <v>63</v>
       </c>
-      <c r="J64" s="9" t="inlineStr"/>
       <c r="K64" s="9" t="inlineStr"/>
-      <c r="L64" s="8" t="inlineStr"/>
-      <c r="M64" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N64" s="10" t="inlineStr"/>
+      <c r="L64" s="9" t="inlineStr"/>
+      <c r="M64" s="8" t="inlineStr"/>
+      <c r="N64" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O64" s="10" t="inlineStr"/>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" s="12" t="inlineStr">
@@ -4091,18 +4190,19 @@
           <t>S11</t>
         </is>
       </c>
-      <c r="I65" s="13" t="n">
+      <c r="I65" s="13" t="inlineStr"/>
+      <c r="J65" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="J65" s="13" t="inlineStr"/>
       <c r="K65" s="13" t="inlineStr"/>
-      <c r="L65" s="12" t="inlineStr"/>
-      <c r="M65" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N65" s="14" t="inlineStr">
+      <c r="L65" s="13" t="inlineStr"/>
+      <c r="M65" s="12" t="inlineStr"/>
+      <c r="N65" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O65" s="14" t="inlineStr">
         <is>
           <t>shared coordinate with SCD-48</t>
         </is>
@@ -4145,18 +4245,19 @@
           <t>S5</t>
         </is>
       </c>
-      <c r="I66" s="9" t="n">
+      <c r="I66" s="9" t="inlineStr"/>
+      <c r="J66" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="J66" s="9" t="inlineStr"/>
       <c r="K66" s="9" t="inlineStr"/>
-      <c r="L66" s="8" t="inlineStr"/>
-      <c r="M66" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N66" s="10" t="inlineStr"/>
+      <c r="L66" s="9" t="inlineStr"/>
+      <c r="M66" s="8" t="inlineStr"/>
+      <c r="N66" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O66" s="10" t="inlineStr"/>
     </row>
     <row r="67" ht="27" customHeight="1">
       <c r="A67" s="12" t="inlineStr">
@@ -4195,18 +4296,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I67" s="13" t="n">
+      <c r="I67" s="13" t="inlineStr"/>
+      <c r="J67" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="J67" s="13" t="inlineStr"/>
       <c r="K67" s="13" t="inlineStr"/>
-      <c r="L67" s="12" t="inlineStr"/>
-      <c r="M67" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N67" s="14" t="inlineStr"/>
+      <c r="L67" s="13" t="inlineStr"/>
+      <c r="M67" s="12" t="inlineStr"/>
+      <c r="N67" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O67" s="14" t="inlineStr"/>
     </row>
     <row r="68" ht="27" customHeight="1">
       <c r="A68" s="8" t="inlineStr">
@@ -4245,18 +4347,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I68" s="9" t="n">
+      <c r="I68" s="9" t="inlineStr"/>
+      <c r="J68" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="J68" s="9" t="inlineStr"/>
       <c r="K68" s="9" t="inlineStr"/>
-      <c r="L68" s="8" t="inlineStr"/>
-      <c r="M68" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N68" s="10" t="inlineStr"/>
+      <c r="L68" s="9" t="inlineStr"/>
+      <c r="M68" s="8" t="inlineStr"/>
+      <c r="N68" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O68" s="10" t="inlineStr"/>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" s="12" t="inlineStr">
@@ -4283,18 +4386,19 @@
       <c r="F69" s="15" t="n"/>
       <c r="G69" s="12" t="inlineStr"/>
       <c r="H69" s="13" t="inlineStr"/>
-      <c r="I69" s="13" t="n">
+      <c r="I69" s="13" t="inlineStr"/>
+      <c r="J69" s="13" t="n">
         <v>150</v>
       </c>
-      <c r="J69" s="13" t="inlineStr"/>
       <c r="K69" s="13" t="inlineStr"/>
-      <c r="L69" s="12" t="inlineStr"/>
-      <c r="M69" s="13" t="inlineStr">
+      <c r="L69" s="13" t="inlineStr"/>
+      <c r="M69" s="12" t="inlineStr"/>
+      <c r="N69" s="13" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="N69" s="14" t="inlineStr">
+      <c r="O69" s="14" t="inlineStr">
         <is>
           <t>No GPS - set PARENT_ID to the tap pole</t>
         </is>
@@ -4325,18 +4429,19 @@
       <c r="F70" s="11" t="n"/>
       <c r="G70" s="8" t="inlineStr"/>
       <c r="H70" s="9" t="inlineStr"/>
-      <c r="I70" s="9" t="n">
+      <c r="I70" s="9" t="inlineStr"/>
+      <c r="J70" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="J70" s="9" t="inlineStr"/>
       <c r="K70" s="9" t="inlineStr"/>
-      <c r="L70" s="8" t="inlineStr"/>
-      <c r="M70" s="9" t="inlineStr">
+      <c r="L70" s="9" t="inlineStr"/>
+      <c r="M70" s="8" t="inlineStr"/>
+      <c r="N70" s="9" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="N70" s="10" t="inlineStr">
+      <c r="O70" s="10" t="inlineStr">
         <is>
           <t>No GPS - set PARENT_ID to the tap pole</t>
         </is>
@@ -4367,18 +4472,19 @@
       <c r="F71" s="15" t="n"/>
       <c r="G71" s="12" t="inlineStr"/>
       <c r="H71" s="13" t="inlineStr"/>
-      <c r="I71" s="13" t="n">
+      <c r="I71" s="13" t="inlineStr"/>
+      <c r="J71" s="13" t="n">
         <v>98</v>
       </c>
-      <c r="J71" s="13" t="inlineStr"/>
       <c r="K71" s="13" t="inlineStr"/>
-      <c r="L71" s="12" t="inlineStr"/>
-      <c r="M71" s="13" t="inlineStr">
+      <c r="L71" s="13" t="inlineStr"/>
+      <c r="M71" s="12" t="inlineStr"/>
+      <c r="N71" s="13" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="N71" s="14" t="inlineStr">
+      <c r="O71" s="14" t="inlineStr">
         <is>
           <t>No GPS - set PARENT_ID to the tap pole</t>
         </is>
@@ -4409,18 +4515,19 @@
       <c r="F72" s="11" t="n"/>
       <c r="G72" s="8" t="inlineStr"/>
       <c r="H72" s="9" t="inlineStr"/>
-      <c r="I72" s="9" t="n">
+      <c r="I72" s="9" t="inlineStr"/>
+      <c r="J72" s="9" t="n">
         <v>70</v>
       </c>
-      <c r="J72" s="9" t="inlineStr"/>
       <c r="K72" s="9" t="inlineStr"/>
-      <c r="L72" s="8" t="inlineStr"/>
-      <c r="M72" s="9" t="inlineStr">
+      <c r="L72" s="9" t="inlineStr"/>
+      <c r="M72" s="8" t="inlineStr"/>
+      <c r="N72" s="9" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="N72" s="10" t="inlineStr">
+      <c r="O72" s="10" t="inlineStr">
         <is>
           <t>No GPS - set PARENT_ID to the tap pole</t>
         </is>
@@ -4451,18 +4558,19 @@
       <c r="F73" s="15" t="n"/>
       <c r="G73" s="12" t="inlineStr"/>
       <c r="H73" s="13" t="inlineStr"/>
-      <c r="I73" s="13" t="n">
+      <c r="I73" s="13" t="inlineStr"/>
+      <c r="J73" s="13" t="n">
         <v>60</v>
       </c>
-      <c r="J73" s="13" t="inlineStr"/>
       <c r="K73" s="13" t="inlineStr"/>
-      <c r="L73" s="12" t="inlineStr"/>
-      <c r="M73" s="13" t="inlineStr">
+      <c r="L73" s="13" t="inlineStr"/>
+      <c r="M73" s="12" t="inlineStr"/>
+      <c r="N73" s="13" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="N73" s="14" t="inlineStr">
+      <c r="O73" s="14" t="inlineStr">
         <is>
           <t>No GPS - set PARENT_ID to the tap pole</t>
         </is>
@@ -4505,18 +4613,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I74" s="9" t="n">
+      <c r="I74" s="9" t="inlineStr"/>
+      <c r="J74" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="J74" s="9" t="inlineStr"/>
       <c r="K74" s="9" t="inlineStr"/>
-      <c r="L74" s="8" t="inlineStr"/>
-      <c r="M74" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N74" s="10" t="inlineStr"/>
+      <c r="L74" s="9" t="inlineStr"/>
+      <c r="M74" s="8" t="inlineStr"/>
+      <c r="N74" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O74" s="10" t="inlineStr"/>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" s="12" t="inlineStr">
@@ -4555,18 +4664,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I75" s="13" t="n">
+      <c r="I75" s="13" t="inlineStr"/>
+      <c r="J75" s="13" t="n">
         <v>250</v>
       </c>
-      <c r="J75" s="13" t="inlineStr"/>
       <c r="K75" s="13" t="inlineStr"/>
-      <c r="L75" s="12" t="inlineStr"/>
-      <c r="M75" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N75" s="14" t="inlineStr"/>
+      <c r="L75" s="13" t="inlineStr"/>
+      <c r="M75" s="12" t="inlineStr"/>
+      <c r="N75" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O75" s="14" t="inlineStr"/>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" s="8" t="inlineStr">
@@ -4605,18 +4715,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I76" s="9" t="n">
+      <c r="I76" s="9" t="inlineStr"/>
+      <c r="J76" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="J76" s="9" t="inlineStr"/>
       <c r="K76" s="9" t="inlineStr"/>
-      <c r="L76" s="8" t="inlineStr"/>
-      <c r="M76" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N76" s="10" t="inlineStr"/>
+      <c r="L76" s="9" t="inlineStr"/>
+      <c r="M76" s="8" t="inlineStr"/>
+      <c r="N76" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O76" s="10" t="inlineStr"/>
     </row>
     <row r="77" ht="15" customHeight="1">
       <c r="A77" s="12" t="inlineStr">
@@ -4655,18 +4766,19 @@
           <t>S6</t>
         </is>
       </c>
-      <c r="I77" s="13" t="n">
+      <c r="I77" s="13" t="inlineStr"/>
+      <c r="J77" s="13" t="n">
         <v>63</v>
       </c>
-      <c r="J77" s="13" t="inlineStr"/>
       <c r="K77" s="13" t="inlineStr"/>
-      <c r="L77" s="12" t="inlineStr"/>
-      <c r="M77" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N77" s="14" t="inlineStr"/>
+      <c r="L77" s="13" t="inlineStr"/>
+      <c r="M77" s="12" t="inlineStr"/>
+      <c r="N77" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O77" s="14" t="inlineStr"/>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="A78" s="8" t="inlineStr">
@@ -4705,18 +4817,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I78" s="9" t="n">
+      <c r="I78" s="9" t="inlineStr"/>
+      <c r="J78" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="J78" s="9" t="inlineStr"/>
       <c r="K78" s="9" t="inlineStr"/>
-      <c r="L78" s="8" t="inlineStr"/>
-      <c r="M78" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N78" s="10" t="inlineStr"/>
+      <c r="L78" s="9" t="inlineStr"/>
+      <c r="M78" s="8" t="inlineStr"/>
+      <c r="N78" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O78" s="10" t="inlineStr"/>
     </row>
     <row r="79" ht="15" customHeight="1">
       <c r="A79" s="12" t="inlineStr">
@@ -4755,18 +4868,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I79" s="13" t="n">
+      <c r="I79" s="13" t="inlineStr"/>
+      <c r="J79" s="13" t="n">
         <v>250</v>
       </c>
-      <c r="J79" s="13" t="inlineStr"/>
       <c r="K79" s="13" t="inlineStr"/>
-      <c r="L79" s="12" t="inlineStr"/>
-      <c r="M79" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N79" s="14" t="inlineStr"/>
+      <c r="L79" s="13" t="inlineStr"/>
+      <c r="M79" s="12" t="inlineStr"/>
+      <c r="N79" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O79" s="14" t="inlineStr"/>
     </row>
     <row r="80" ht="15" customHeight="1">
       <c r="A80" s="8" t="inlineStr">
@@ -4805,18 +4919,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I80" s="9" t="n">
+      <c r="I80" s="9" t="inlineStr"/>
+      <c r="J80" s="9" t="n">
         <v>63</v>
       </c>
-      <c r="J80" s="9" t="inlineStr"/>
       <c r="K80" s="9" t="inlineStr"/>
-      <c r="L80" s="8" t="inlineStr"/>
-      <c r="M80" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N80" s="10" t="inlineStr"/>
+      <c r="L80" s="9" t="inlineStr"/>
+      <c r="M80" s="8" t="inlineStr"/>
+      <c r="N80" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O80" s="10" t="inlineStr"/>
     </row>
     <row r="81" ht="15" customHeight="1">
       <c r="A81" s="12" t="inlineStr">
@@ -4855,18 +4970,19 @@
           <t>S2</t>
         </is>
       </c>
-      <c r="I81" s="13" t="n">
+      <c r="I81" s="13" t="inlineStr"/>
+      <c r="J81" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="J81" s="13" t="inlineStr"/>
       <c r="K81" s="13" t="inlineStr"/>
-      <c r="L81" s="12" t="inlineStr"/>
-      <c r="M81" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N81" s="14" t="inlineStr"/>
+      <c r="L81" s="13" t="inlineStr"/>
+      <c r="M81" s="12" t="inlineStr"/>
+      <c r="N81" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O81" s="14" t="inlineStr"/>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="A82" s="8" t="inlineStr">
@@ -4905,18 +5021,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I82" s="9" t="n">
+      <c r="I82" s="9" t="inlineStr"/>
+      <c r="J82" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="J82" s="9" t="inlineStr"/>
       <c r="K82" s="9" t="inlineStr"/>
-      <c r="L82" s="8" t="inlineStr"/>
-      <c r="M82" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N82" s="10" t="inlineStr"/>
+      <c r="L82" s="9" t="inlineStr"/>
+      <c r="M82" s="8" t="inlineStr"/>
+      <c r="N82" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O82" s="10" t="inlineStr"/>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" s="12" t="inlineStr">
@@ -4955,18 +5072,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I83" s="13" t="n">
+      <c r="I83" s="13" t="inlineStr"/>
+      <c r="J83" s="13" t="n">
         <v>250</v>
       </c>
-      <c r="J83" s="13" t="inlineStr"/>
       <c r="K83" s="13" t="inlineStr"/>
-      <c r="L83" s="12" t="inlineStr"/>
-      <c r="M83" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N83" s="14" t="inlineStr"/>
+      <c r="L83" s="13" t="inlineStr"/>
+      <c r="M83" s="12" t="inlineStr"/>
+      <c r="N83" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O83" s="14" t="inlineStr"/>
     </row>
     <row r="84" ht="15" customHeight="1">
       <c r="A84" s="8" t="inlineStr">
@@ -5005,18 +5123,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I84" s="9" t="n">
+      <c r="I84" s="9" t="inlineStr"/>
+      <c r="J84" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="J84" s="9" t="inlineStr"/>
       <c r="K84" s="9" t="inlineStr"/>
-      <c r="L84" s="8" t="inlineStr"/>
-      <c r="M84" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N84" s="10" t="inlineStr"/>
+      <c r="L84" s="9" t="inlineStr"/>
+      <c r="M84" s="8" t="inlineStr"/>
+      <c r="N84" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O84" s="10" t="inlineStr"/>
     </row>
     <row r="85" ht="15" customHeight="1">
       <c r="A85" s="12" t="inlineStr">
@@ -5055,18 +5174,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I85" s="13" t="n">
+      <c r="I85" s="13" t="inlineStr"/>
+      <c r="J85" s="13" t="n">
         <v>250</v>
       </c>
-      <c r="J85" s="13" t="inlineStr"/>
       <c r="K85" s="13" t="inlineStr"/>
-      <c r="L85" s="12" t="inlineStr"/>
-      <c r="M85" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N85" s="14" t="inlineStr"/>
+      <c r="L85" s="13" t="inlineStr"/>
+      <c r="M85" s="12" t="inlineStr"/>
+      <c r="N85" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O85" s="14" t="inlineStr"/>
     </row>
     <row r="86" ht="15" customHeight="1">
       <c r="A86" s="8" t="inlineStr">
@@ -5105,18 +5225,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I86" s="9" t="n">
+      <c r="I86" s="9" t="inlineStr"/>
+      <c r="J86" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="J86" s="9" t="inlineStr"/>
       <c r="K86" s="9" t="inlineStr"/>
-      <c r="L86" s="8" t="inlineStr"/>
-      <c r="M86" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N86" s="10" t="inlineStr"/>
+      <c r="L86" s="9" t="inlineStr"/>
+      <c r="M86" s="8" t="inlineStr"/>
+      <c r="N86" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O86" s="10" t="inlineStr"/>
     </row>
     <row r="87" ht="15" customHeight="1">
       <c r="A87" s="12" t="inlineStr">
@@ -5155,18 +5276,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I87" s="13" t="n">
+      <c r="I87" s="13" t="inlineStr"/>
+      <c r="J87" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="J87" s="13" t="inlineStr"/>
       <c r="K87" s="13" t="inlineStr"/>
-      <c r="L87" s="12" t="inlineStr"/>
-      <c r="M87" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N87" s="14" t="inlineStr"/>
+      <c r="L87" s="13" t="inlineStr"/>
+      <c r="M87" s="12" t="inlineStr"/>
+      <c r="N87" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O87" s="14" t="inlineStr"/>
     </row>
     <row r="88" ht="15" customHeight="1">
       <c r="A88" s="8" t="inlineStr">
@@ -5205,18 +5327,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I88" s="9" t="n">
+      <c r="I88" s="9" t="inlineStr"/>
+      <c r="J88" s="9" t="n">
         <v>63</v>
       </c>
-      <c r="J88" s="9" t="inlineStr"/>
       <c r="K88" s="9" t="inlineStr"/>
-      <c r="L88" s="8" t="inlineStr"/>
-      <c r="M88" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N88" s="10" t="inlineStr"/>
+      <c r="L88" s="9" t="inlineStr"/>
+      <c r="M88" s="8" t="inlineStr"/>
+      <c r="N88" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O88" s="10" t="inlineStr"/>
     </row>
     <row r="89" ht="15" customHeight="1">
       <c r="A89" s="12" t="inlineStr">
@@ -5255,18 +5378,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I89" s="13" t="n">
+      <c r="I89" s="13" t="inlineStr"/>
+      <c r="J89" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="J89" s="13" t="inlineStr"/>
       <c r="K89" s="13" t="inlineStr"/>
-      <c r="L89" s="12" t="inlineStr"/>
-      <c r="M89" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N89" s="14" t="inlineStr"/>
+      <c r="L89" s="13" t="inlineStr"/>
+      <c r="M89" s="12" t="inlineStr"/>
+      <c r="N89" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O89" s="14" t="inlineStr"/>
     </row>
     <row r="90" ht="15" customHeight="1">
       <c r="A90" s="8" t="inlineStr">
@@ -5305,18 +5429,19 @@
           <t>S4</t>
         </is>
       </c>
-      <c r="I90" s="9" t="n">
+      <c r="I90" s="9" t="inlineStr"/>
+      <c r="J90" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="J90" s="9" t="inlineStr"/>
       <c r="K90" s="9" t="inlineStr"/>
-      <c r="L90" s="8" t="inlineStr"/>
-      <c r="M90" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N90" s="10" t="inlineStr"/>
+      <c r="L90" s="9" t="inlineStr"/>
+      <c r="M90" s="8" t="inlineStr"/>
+      <c r="N90" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O90" s="10" t="inlineStr"/>
     </row>
     <row r="91" ht="15" customHeight="1">
       <c r="A91" s="12" t="inlineStr">
@@ -5355,18 +5480,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I91" s="13" t="n">
+      <c r="I91" s="13" t="inlineStr"/>
+      <c r="J91" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="J91" s="13" t="inlineStr"/>
       <c r="K91" s="13" t="inlineStr"/>
-      <c r="L91" s="12" t="inlineStr"/>
-      <c r="M91" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N91" s="14" t="inlineStr"/>
+      <c r="L91" s="13" t="inlineStr"/>
+      <c r="M91" s="12" t="inlineStr"/>
+      <c r="N91" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O91" s="14" t="inlineStr"/>
     </row>
     <row r="92" ht="15" customHeight="1">
       <c r="A92" s="8" t="inlineStr">
@@ -5405,18 +5531,19 @@
           <t>S3</t>
         </is>
       </c>
-      <c r="I92" s="9" t="n">
+      <c r="I92" s="9" t="inlineStr"/>
+      <c r="J92" s="9" t="n">
         <v>63</v>
       </c>
-      <c r="J92" s="9" t="inlineStr"/>
       <c r="K92" s="9" t="inlineStr"/>
-      <c r="L92" s="8" t="inlineStr"/>
-      <c r="M92" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N92" s="10" t="inlineStr"/>
+      <c r="L92" s="9" t="inlineStr"/>
+      <c r="M92" s="8" t="inlineStr"/>
+      <c r="N92" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O92" s="10" t="inlineStr"/>
     </row>
     <row r="93" ht="15" customHeight="1">
       <c r="A93" s="12" t="inlineStr">
@@ -5455,18 +5582,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I93" s="13" t="n">
+      <c r="I93" s="13" t="inlineStr"/>
+      <c r="J93" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="J93" s="13" t="inlineStr"/>
       <c r="K93" s="13" t="inlineStr"/>
-      <c r="L93" s="12" t="inlineStr"/>
-      <c r="M93" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N93" s="14" t="inlineStr"/>
+      <c r="L93" s="13" t="inlineStr"/>
+      <c r="M93" s="12" t="inlineStr"/>
+      <c r="N93" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O93" s="14" t="inlineStr"/>
     </row>
     <row r="94" ht="15" customHeight="1">
       <c r="A94" s="8" t="inlineStr">
@@ -5505,18 +5633,19 @@
           <t>S1</t>
         </is>
       </c>
-      <c r="I94" s="9" t="n">
+      <c r="I94" s="9" t="inlineStr"/>
+      <c r="J94" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="J94" s="9" t="inlineStr"/>
       <c r="K94" s="9" t="inlineStr"/>
-      <c r="L94" s="8" t="inlineStr"/>
-      <c r="M94" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N94" s="10" t="inlineStr"/>
+      <c r="L94" s="9" t="inlineStr"/>
+      <c r="M94" s="8" t="inlineStr"/>
+      <c r="N94" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O94" s="10" t="inlineStr"/>
     </row>
     <row r="95" ht="15" customHeight="1">
       <c r="A95" s="12" t="inlineStr">
@@ -5555,18 +5684,19 @@
           <t>S1</t>
         </is>
       </c>
-      <c r="I95" s="13" t="n">
+      <c r="I95" s="13" t="inlineStr"/>
+      <c r="J95" s="13" t="n">
         <v>63</v>
       </c>
-      <c r="J95" s="13" t="inlineStr"/>
       <c r="K95" s="13" t="inlineStr"/>
-      <c r="L95" s="12" t="inlineStr"/>
-      <c r="M95" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N95" s="14" t="inlineStr"/>
+      <c r="L95" s="13" t="inlineStr"/>
+      <c r="M95" s="12" t="inlineStr"/>
+      <c r="N95" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O95" s="14" t="inlineStr"/>
     </row>
     <row r="96" ht="15" customHeight="1">
       <c r="A96" s="8" t="inlineStr">
@@ -5605,18 +5735,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I96" s="9" t="n">
+      <c r="I96" s="9" t="inlineStr"/>
+      <c r="J96" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="J96" s="9" t="inlineStr"/>
       <c r="K96" s="9" t="inlineStr"/>
-      <c r="L96" s="8" t="inlineStr"/>
-      <c r="M96" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N96" s="10" t="inlineStr"/>
+      <c r="L96" s="9" t="inlineStr"/>
+      <c r="M96" s="8" t="inlineStr"/>
+      <c r="N96" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O96" s="10" t="inlineStr"/>
     </row>
     <row r="97" ht="15" customHeight="1">
       <c r="A97" s="12" t="inlineStr">
@@ -5655,18 +5786,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I97" s="13" t="n">
+      <c r="I97" s="13" t="inlineStr"/>
+      <c r="J97" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="J97" s="13" t="inlineStr"/>
       <c r="K97" s="13" t="inlineStr"/>
-      <c r="L97" s="12" t="inlineStr"/>
-      <c r="M97" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N97" s="14" t="inlineStr"/>
+      <c r="L97" s="13" t="inlineStr"/>
+      <c r="M97" s="12" t="inlineStr"/>
+      <c r="N97" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O97" s="14" t="inlineStr"/>
     </row>
     <row r="98" ht="15" customHeight="1">
       <c r="A98" s="8" t="inlineStr">
@@ -5693,18 +5825,19 @@
       <c r="F98" s="11" t="n"/>
       <c r="G98" s="8" t="inlineStr"/>
       <c r="H98" s="9" t="inlineStr"/>
-      <c r="I98" s="9" t="n">
+      <c r="I98" s="9" t="inlineStr"/>
+      <c r="J98" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="J98" s="9" t="inlineStr"/>
       <c r="K98" s="9" t="inlineStr"/>
-      <c r="L98" s="8" t="inlineStr"/>
-      <c r="M98" s="9" t="inlineStr">
+      <c r="L98" s="9" t="inlineStr"/>
+      <c r="M98" s="8" t="inlineStr"/>
+      <c r="N98" s="9" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="N98" s="10" t="inlineStr">
+      <c r="O98" s="10" t="inlineStr">
         <is>
           <t>no usable GPS - set PARENT_ID by hand</t>
         </is>
@@ -5747,18 +5880,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I99" s="13" t="n">
+      <c r="I99" s="13" t="inlineStr"/>
+      <c r="J99" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="J99" s="13" t="inlineStr"/>
       <c r="K99" s="13" t="inlineStr"/>
-      <c r="L99" s="12" t="inlineStr"/>
-      <c r="M99" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N99" s="14" t="inlineStr"/>
+      <c r="L99" s="13" t="inlineStr"/>
+      <c r="M99" s="12" t="inlineStr"/>
+      <c r="N99" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O99" s="14" t="inlineStr"/>
     </row>
     <row r="100" ht="15" customHeight="1">
       <c r="A100" s="8" t="inlineStr">
@@ -5797,18 +5931,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I100" s="9" t="n">
+      <c r="I100" s="9" t="inlineStr"/>
+      <c r="J100" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="J100" s="9" t="inlineStr"/>
       <c r="K100" s="9" t="inlineStr"/>
-      <c r="L100" s="8" t="inlineStr"/>
-      <c r="M100" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N100" s="10" t="inlineStr"/>
+      <c r="L100" s="9" t="inlineStr"/>
+      <c r="M100" s="8" t="inlineStr"/>
+      <c r="N100" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O100" s="10" t="inlineStr"/>
     </row>
     <row r="101" ht="15" customHeight="1">
       <c r="A101" s="12" t="inlineStr">
@@ -5847,18 +5982,19 @@
           <t>S3</t>
         </is>
       </c>
-      <c r="I101" s="13" t="n">
+      <c r="I101" s="13" t="inlineStr"/>
+      <c r="J101" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="J101" s="13" t="inlineStr"/>
       <c r="K101" s="13" t="inlineStr"/>
-      <c r="L101" s="12" t="inlineStr"/>
-      <c r="M101" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N101" s="14" t="inlineStr"/>
+      <c r="L101" s="13" t="inlineStr"/>
+      <c r="M101" s="12" t="inlineStr"/>
+      <c r="N101" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O101" s="14" t="inlineStr"/>
     </row>
     <row r="102" ht="15" customHeight="1">
       <c r="A102" s="8" t="inlineStr">
@@ -5897,18 +6033,19 @@
           <t>S5</t>
         </is>
       </c>
-      <c r="I102" s="9" t="n">
+      <c r="I102" s="9" t="inlineStr"/>
+      <c r="J102" s="9" t="n">
         <v>63</v>
       </c>
-      <c r="J102" s="9" t="inlineStr"/>
       <c r="K102" s="9" t="inlineStr"/>
-      <c r="L102" s="8" t="inlineStr"/>
-      <c r="M102" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N102" s="10" t="inlineStr"/>
+      <c r="L102" s="9" t="inlineStr"/>
+      <c r="M102" s="8" t="inlineStr"/>
+      <c r="N102" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O102" s="10" t="inlineStr"/>
     </row>
     <row r="103" ht="15" customHeight="1">
       <c r="A103" s="12" t="inlineStr">
@@ -5947,18 +6084,19 @@
           <t>S5</t>
         </is>
       </c>
-      <c r="I103" s="13" t="n">
+      <c r="I103" s="13" t="inlineStr"/>
+      <c r="J103" s="13" t="n">
         <v>63</v>
       </c>
-      <c r="J103" s="13" t="inlineStr"/>
       <c r="K103" s="13" t="inlineStr"/>
-      <c r="L103" s="12" t="inlineStr"/>
-      <c r="M103" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N103" s="14" t="inlineStr"/>
+      <c r="L103" s="13" t="inlineStr"/>
+      <c r="M103" s="12" t="inlineStr"/>
+      <c r="N103" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O103" s="14" t="inlineStr"/>
     </row>
     <row r="104" ht="15" customHeight="1">
       <c r="A104" s="8" t="inlineStr">
@@ -5985,18 +6123,19 @@
       <c r="F104" s="11" t="n"/>
       <c r="G104" s="8" t="inlineStr"/>
       <c r="H104" s="9" t="inlineStr"/>
-      <c r="I104" s="9" t="n">
+      <c r="I104" s="9" t="inlineStr"/>
+      <c r="J104" s="9" t="n">
         <v>63</v>
       </c>
-      <c r="J104" s="9" t="inlineStr"/>
       <c r="K104" s="9" t="inlineStr"/>
-      <c r="L104" s="8" t="inlineStr"/>
-      <c r="M104" s="9" t="inlineStr">
+      <c r="L104" s="9" t="inlineStr"/>
+      <c r="M104" s="8" t="inlineStr"/>
+      <c r="N104" s="9" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="N104" s="10" t="inlineStr">
+      <c r="O104" s="10" t="inlineStr">
         <is>
           <t>no usable GPS - set PARENT_ID by hand</t>
         </is>
@@ -6027,18 +6166,19 @@
       <c r="F105" s="15" t="n"/>
       <c r="G105" s="12" t="inlineStr"/>
       <c r="H105" s="13" t="inlineStr"/>
-      <c r="I105" s="13" t="n">
+      <c r="I105" s="13" t="inlineStr"/>
+      <c r="J105" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="J105" s="13" t="inlineStr"/>
       <c r="K105" s="13" t="inlineStr"/>
-      <c r="L105" s="12" t="inlineStr"/>
-      <c r="M105" s="13" t="inlineStr">
+      <c r="L105" s="13" t="inlineStr"/>
+      <c r="M105" s="12" t="inlineStr"/>
+      <c r="N105" s="13" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="N105" s="14" t="inlineStr">
+      <c r="O105" s="14" t="inlineStr">
         <is>
           <t>no usable GPS - set PARENT_ID by hand</t>
         </is>
@@ -6069,18 +6209,19 @@
       <c r="F106" s="11" t="n"/>
       <c r="G106" s="8" t="inlineStr"/>
       <c r="H106" s="9" t="inlineStr"/>
-      <c r="I106" s="9" t="n">
+      <c r="I106" s="9" t="inlineStr"/>
+      <c r="J106" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="J106" s="9" t="inlineStr"/>
       <c r="K106" s="9" t="inlineStr"/>
-      <c r="L106" s="8" t="inlineStr"/>
-      <c r="M106" s="9" t="inlineStr">
+      <c r="L106" s="9" t="inlineStr"/>
+      <c r="M106" s="8" t="inlineStr"/>
+      <c r="N106" s="9" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="N106" s="10" t="inlineStr">
+      <c r="O106" s="10" t="inlineStr">
         <is>
           <t>no usable GPS - set PARENT_ID by hand</t>
         </is>
@@ -6123,18 +6264,19 @@
           <t>S3</t>
         </is>
       </c>
-      <c r="I107" s="13" t="n">
+      <c r="I107" s="13" t="inlineStr"/>
+      <c r="J107" s="13" t="n">
         <v>250</v>
       </c>
-      <c r="J107" s="13" t="inlineStr"/>
       <c r="K107" s="13" t="inlineStr"/>
-      <c r="L107" s="12" t="inlineStr"/>
-      <c r="M107" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N107" s="14" t="inlineStr"/>
+      <c r="L107" s="13" t="inlineStr"/>
+      <c r="M107" s="12" t="inlineStr"/>
+      <c r="N107" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O107" s="14" t="inlineStr"/>
     </row>
     <row r="108" ht="15" customHeight="1">
       <c r="A108" s="8" t="inlineStr">
@@ -6161,18 +6303,19 @@
       <c r="F108" s="11" t="n"/>
       <c r="G108" s="8" t="inlineStr"/>
       <c r="H108" s="9" t="inlineStr"/>
-      <c r="I108" s="9" t="n">
+      <c r="I108" s="9" t="inlineStr"/>
+      <c r="J108" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="J108" s="9" t="inlineStr"/>
       <c r="K108" s="9" t="inlineStr"/>
-      <c r="L108" s="8" t="inlineStr"/>
-      <c r="M108" s="9" t="inlineStr">
+      <c r="L108" s="9" t="inlineStr"/>
+      <c r="M108" s="8" t="inlineStr"/>
+      <c r="N108" s="9" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="N108" s="10" t="inlineStr">
+      <c r="O108" s="10" t="inlineStr">
         <is>
           <t>no usable GPS - set PARENT_ID by hand</t>
         </is>
@@ -6215,18 +6358,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I109" s="13" t="n">
+      <c r="I109" s="13" t="inlineStr"/>
+      <c r="J109" s="13" t="n">
         <v>250</v>
       </c>
-      <c r="J109" s="13" t="inlineStr"/>
       <c r="K109" s="13" t="inlineStr"/>
-      <c r="L109" s="12" t="inlineStr"/>
-      <c r="M109" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N109" s="14" t="inlineStr"/>
+      <c r="L109" s="13" t="inlineStr"/>
+      <c r="M109" s="12" t="inlineStr"/>
+      <c r="N109" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O109" s="14" t="inlineStr"/>
     </row>
     <row r="110" ht="15" customHeight="1">
       <c r="A110" s="8" t="inlineStr">
@@ -6265,18 +6409,19 @@
           <t>S1</t>
         </is>
       </c>
-      <c r="I110" s="9" t="n">
+      <c r="I110" s="9" t="inlineStr"/>
+      <c r="J110" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="J110" s="9" t="inlineStr"/>
       <c r="K110" s="9" t="inlineStr"/>
-      <c r="L110" s="8" t="inlineStr"/>
-      <c r="M110" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N110" s="10" t="inlineStr"/>
+      <c r="L110" s="9" t="inlineStr"/>
+      <c r="M110" s="8" t="inlineStr"/>
+      <c r="N110" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O110" s="10" t="inlineStr"/>
     </row>
     <row r="111" ht="15" customHeight="1">
       <c r="A111" s="12" t="inlineStr">
@@ -6315,18 +6460,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I111" s="13" t="n">
+      <c r="I111" s="13" t="inlineStr"/>
+      <c r="J111" s="13" t="n">
         <v>250</v>
       </c>
-      <c r="J111" s="13" t="inlineStr"/>
       <c r="K111" s="13" t="inlineStr"/>
-      <c r="L111" s="12" t="inlineStr"/>
-      <c r="M111" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N111" s="14" t="inlineStr"/>
+      <c r="L111" s="13" t="inlineStr"/>
+      <c r="M111" s="12" t="inlineStr"/>
+      <c r="N111" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O111" s="14" t="inlineStr"/>
     </row>
     <row r="112" ht="15" customHeight="1">
       <c r="A112" s="8" t="inlineStr">
@@ -6365,18 +6511,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I112" s="9" t="n">
+      <c r="I112" s="9" t="inlineStr"/>
+      <c r="J112" s="9" t="n">
         <v>63</v>
       </c>
-      <c r="J112" s="9" t="inlineStr"/>
       <c r="K112" s="9" t="inlineStr"/>
-      <c r="L112" s="8" t="inlineStr"/>
-      <c r="M112" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N112" s="10" t="inlineStr"/>
+      <c r="L112" s="9" t="inlineStr"/>
+      <c r="M112" s="8" t="inlineStr"/>
+      <c r="N112" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O112" s="10" t="inlineStr"/>
     </row>
     <row r="113" ht="15" customHeight="1">
       <c r="A113" s="12" t="inlineStr">
@@ -6415,18 +6562,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I113" s="13" t="n">
+      <c r="I113" s="13" t="inlineStr"/>
+      <c r="J113" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="J113" s="13" t="inlineStr"/>
       <c r="K113" s="13" t="inlineStr"/>
-      <c r="L113" s="12" t="inlineStr"/>
-      <c r="M113" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N113" s="14" t="inlineStr"/>
+      <c r="L113" s="13" t="inlineStr"/>
+      <c r="M113" s="12" t="inlineStr"/>
+      <c r="N113" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O113" s="14" t="inlineStr"/>
     </row>
     <row r="114" ht="15" customHeight="1">
       <c r="A114" s="8" t="inlineStr">
@@ -6465,18 +6613,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I114" s="9" t="n">
+      <c r="I114" s="9" t="inlineStr"/>
+      <c r="J114" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="J114" s="9" t="inlineStr"/>
       <c r="K114" s="9" t="inlineStr"/>
-      <c r="L114" s="8" t="inlineStr"/>
-      <c r="M114" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N114" s="10" t="inlineStr"/>
+      <c r="L114" s="9" t="inlineStr"/>
+      <c r="M114" s="8" t="inlineStr"/>
+      <c r="N114" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O114" s="10" t="inlineStr"/>
     </row>
     <row r="115" ht="15" customHeight="1">
       <c r="A115" s="12" t="inlineStr">
@@ -6515,18 +6664,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I115" s="13" t="n">
+      <c r="I115" s="13" t="inlineStr"/>
+      <c r="J115" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="J115" s="13" t="inlineStr"/>
       <c r="K115" s="13" t="inlineStr"/>
-      <c r="L115" s="12" t="inlineStr"/>
-      <c r="M115" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N115" s="14" t="inlineStr"/>
+      <c r="L115" s="13" t="inlineStr"/>
+      <c r="M115" s="12" t="inlineStr"/>
+      <c r="N115" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O115" s="14" t="inlineStr"/>
     </row>
     <row r="116" ht="15" customHeight="1">
       <c r="A116" s="8" t="inlineStr">
@@ -6565,18 +6715,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I116" s="9" t="n">
+      <c r="I116" s="9" t="inlineStr"/>
+      <c r="J116" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="J116" s="9" t="inlineStr"/>
       <c r="K116" s="9" t="inlineStr"/>
-      <c r="L116" s="8" t="inlineStr"/>
-      <c r="M116" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N116" s="10" t="inlineStr"/>
+      <c r="L116" s="9" t="inlineStr"/>
+      <c r="M116" s="8" t="inlineStr"/>
+      <c r="N116" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O116" s="10" t="inlineStr"/>
     </row>
     <row r="117" ht="15" customHeight="1">
       <c r="A117" s="12" t="inlineStr">
@@ -6615,18 +6766,19 @@
           <t>S3</t>
         </is>
       </c>
-      <c r="I117" s="13" t="n">
+      <c r="I117" s="13" t="inlineStr"/>
+      <c r="J117" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="J117" s="13" t="inlineStr"/>
       <c r="K117" s="13" t="inlineStr"/>
-      <c r="L117" s="12" t="inlineStr"/>
-      <c r="M117" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N117" s="14" t="inlineStr"/>
+      <c r="L117" s="13" t="inlineStr"/>
+      <c r="M117" s="12" t="inlineStr"/>
+      <c r="N117" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O117" s="14" t="inlineStr"/>
     </row>
     <row r="118" ht="15" customHeight="1">
       <c r="A118" s="8" t="inlineStr">
@@ -6665,18 +6817,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I118" s="9" t="n">
+      <c r="I118" s="9" t="inlineStr"/>
+      <c r="J118" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="J118" s="9" t="inlineStr"/>
       <c r="K118" s="9" t="inlineStr"/>
-      <c r="L118" s="8" t="inlineStr"/>
-      <c r="M118" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N118" s="10" t="inlineStr"/>
+      <c r="L118" s="9" t="inlineStr"/>
+      <c r="M118" s="8" t="inlineStr"/>
+      <c r="N118" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O118" s="10" t="inlineStr"/>
     </row>
     <row r="119" ht="15" customHeight="1">
       <c r="A119" s="12" t="inlineStr">
@@ -6715,18 +6868,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I119" s="13" t="n">
+      <c r="I119" s="13" t="inlineStr"/>
+      <c r="J119" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="J119" s="13" t="inlineStr"/>
       <c r="K119" s="13" t="inlineStr"/>
-      <c r="L119" s="12" t="inlineStr"/>
-      <c r="M119" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N119" s="14" t="inlineStr"/>
+      <c r="L119" s="13" t="inlineStr"/>
+      <c r="M119" s="12" t="inlineStr"/>
+      <c r="N119" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O119" s="14" t="inlineStr"/>
     </row>
     <row r="120" ht="15" customHeight="1">
       <c r="A120" s="8" t="inlineStr">
@@ -6765,18 +6919,19 @@
           <t>S3</t>
         </is>
       </c>
-      <c r="I120" s="9" t="n">
+      <c r="I120" s="9" t="inlineStr"/>
+      <c r="J120" s="9" t="n">
         <v>63</v>
       </c>
-      <c r="J120" s="9" t="inlineStr"/>
       <c r="K120" s="9" t="inlineStr"/>
-      <c r="L120" s="8" t="inlineStr"/>
-      <c r="M120" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N120" s="10" t="inlineStr"/>
+      <c r="L120" s="9" t="inlineStr"/>
+      <c r="M120" s="8" t="inlineStr"/>
+      <c r="N120" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O120" s="10" t="inlineStr"/>
     </row>
     <row r="121" ht="15" customHeight="1">
       <c r="A121" s="12" t="inlineStr">
@@ -6815,18 +6970,19 @@
           <t>S2</t>
         </is>
       </c>
-      <c r="I121" s="13" t="n">
+      <c r="I121" s="13" t="inlineStr"/>
+      <c r="J121" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="J121" s="13" t="inlineStr"/>
       <c r="K121" s="13" t="inlineStr"/>
-      <c r="L121" s="12" t="inlineStr"/>
-      <c r="M121" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N121" s="14" t="inlineStr"/>
+      <c r="L121" s="13" t="inlineStr"/>
+      <c r="M121" s="12" t="inlineStr"/>
+      <c r="N121" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O121" s="14" t="inlineStr"/>
     </row>
     <row r="122" ht="15" customHeight="1">
       <c r="A122" s="8" t="inlineStr">
@@ -6865,18 +7021,19 @@
           <t>S3</t>
         </is>
       </c>
-      <c r="I122" s="9" t="n">
+      <c r="I122" s="9" t="inlineStr"/>
+      <c r="J122" s="9" t="n">
         <v>63</v>
       </c>
-      <c r="J122" s="9" t="inlineStr"/>
       <c r="K122" s="9" t="inlineStr"/>
-      <c r="L122" s="8" t="inlineStr"/>
-      <c r="M122" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N122" s="10" t="inlineStr"/>
+      <c r="L122" s="9" t="inlineStr"/>
+      <c r="M122" s="8" t="inlineStr"/>
+      <c r="N122" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O122" s="10" t="inlineStr"/>
     </row>
     <row r="123" ht="15" customHeight="1">
       <c r="A123" s="12" t="inlineStr">
@@ -6915,18 +7072,19 @@
           <t>S3</t>
         </is>
       </c>
-      <c r="I123" s="13" t="n">
+      <c r="I123" s="13" t="inlineStr"/>
+      <c r="J123" s="13" t="n">
         <v>63</v>
       </c>
-      <c r="J123" s="13" t="inlineStr"/>
       <c r="K123" s="13" t="inlineStr"/>
-      <c r="L123" s="12" t="inlineStr"/>
-      <c r="M123" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N123" s="14" t="inlineStr"/>
+      <c r="L123" s="13" t="inlineStr"/>
+      <c r="M123" s="12" t="inlineStr"/>
+      <c r="N123" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O123" s="14" t="inlineStr"/>
     </row>
     <row r="124" ht="27" customHeight="1">
       <c r="A124" s="8" t="inlineStr">
@@ -6965,18 +7123,19 @@
           <t>S3</t>
         </is>
       </c>
-      <c r="I124" s="9" t="n">
+      <c r="I124" s="9" t="inlineStr"/>
+      <c r="J124" s="9" t="n">
         <v>63</v>
       </c>
-      <c r="J124" s="9" t="inlineStr"/>
       <c r="K124" s="9" t="inlineStr"/>
-      <c r="L124" s="8" t="inlineStr"/>
-      <c r="M124" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N124" s="10" t="inlineStr"/>
+      <c r="L124" s="9" t="inlineStr"/>
+      <c r="M124" s="8" t="inlineStr"/>
+      <c r="N124" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O124" s="10" t="inlineStr"/>
     </row>
     <row r="125" ht="15" customHeight="1">
       <c r="A125" s="12" t="inlineStr">
@@ -7003,18 +7162,19 @@
       <c r="F125" s="15" t="n"/>
       <c r="G125" s="12" t="inlineStr"/>
       <c r="H125" s="13" t="inlineStr"/>
-      <c r="I125" s="13" t="n">
+      <c r="I125" s="13" t="inlineStr"/>
+      <c r="J125" s="13" t="n">
         <v>250</v>
       </c>
-      <c r="J125" s="13" t="inlineStr"/>
       <c r="K125" s="13" t="inlineStr"/>
-      <c r="L125" s="12" t="inlineStr"/>
-      <c r="M125" s="13" t="inlineStr">
+      <c r="L125" s="13" t="inlineStr"/>
+      <c r="M125" s="12" t="inlineStr"/>
+      <c r="N125" s="13" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="N125" s="14" t="inlineStr">
+      <c r="O125" s="14" t="inlineStr">
         <is>
           <t>no usable GPS - set PARENT_ID by hand</t>
         </is>
@@ -7057,18 +7217,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I126" s="9" t="n">
+      <c r="I126" s="9" t="inlineStr"/>
+      <c r="J126" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="J126" s="9" t="inlineStr"/>
       <c r="K126" s="9" t="inlineStr"/>
-      <c r="L126" s="8" t="inlineStr"/>
-      <c r="M126" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N126" s="10" t="inlineStr"/>
+      <c r="L126" s="9" t="inlineStr"/>
+      <c r="M126" s="8" t="inlineStr"/>
+      <c r="N126" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O126" s="10" t="inlineStr"/>
     </row>
     <row r="127" ht="15" customHeight="1">
       <c r="A127" s="12" t="inlineStr">
@@ -7107,18 +7268,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I127" s="13" t="n">
+      <c r="I127" s="13" t="inlineStr"/>
+      <c r="J127" s="13" t="n">
         <v>250</v>
       </c>
-      <c r="J127" s="13" t="inlineStr"/>
       <c r="K127" s="13" t="inlineStr"/>
-      <c r="L127" s="12" t="inlineStr"/>
-      <c r="M127" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N127" s="14" t="inlineStr"/>
+      <c r="L127" s="13" t="inlineStr"/>
+      <c r="M127" s="12" t="inlineStr"/>
+      <c r="N127" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O127" s="14" t="inlineStr"/>
     </row>
     <row r="128" ht="15" customHeight="1">
       <c r="A128" s="8" t="inlineStr">
@@ -7157,18 +7319,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I128" s="9" t="n">
+      <c r="I128" s="9" t="inlineStr"/>
+      <c r="J128" s="9" t="n">
         <v>63</v>
       </c>
-      <c r="J128" s="9" t="inlineStr"/>
       <c r="K128" s="9" t="inlineStr"/>
-      <c r="L128" s="8" t="inlineStr"/>
-      <c r="M128" s="9" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N128" s="10" t="inlineStr"/>
+      <c r="L128" s="9" t="inlineStr"/>
+      <c r="M128" s="8" t="inlineStr"/>
+      <c r="N128" s="9" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O128" s="10" t="inlineStr"/>
     </row>
     <row r="129" ht="15" customHeight="1">
       <c r="A129" s="12" t="inlineStr">
@@ -7207,30 +7370,31 @@
           <t>T</t>
         </is>
       </c>
-      <c r="I129" s="13" t="n">
+      <c r="I129" s="13" t="inlineStr"/>
+      <c r="J129" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="J129" s="13" t="inlineStr"/>
       <c r="K129" s="13" t="inlineStr"/>
-      <c r="L129" s="12" t="inlineStr"/>
-      <c r="M129" s="13" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
-        </is>
-      </c>
-      <c r="N129" s="14" t="inlineStr"/>
+      <c r="L129" s="13" t="inlineStr"/>
+      <c r="M129" s="12" t="inlineStr"/>
+      <c r="N129" s="13" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="O129" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N129"/>
-  <conditionalFormatting sqref="M2:M129">
+  <autoFilter ref="A1:O129"/>
+  <conditionalFormatting sqref="N2:N129">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$M2="INFERRED"</formula>
+      <formula>$N2="INFERRED"</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>$M2="UNKNOWN"</formula>
+      <formula>$N2="UNKNOWN"</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="2">
-      <formula>OR($M2="SURVEYED",$M2="FROM-SLD")</formula>
+      <formula>OR($N2="SURVEYED",$N2="FROM-SLD")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G129">
@@ -7238,18 +7402,26 @@
       <formula>AND($B2&lt;&gt;"MUSS",$G2="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
+  <conditionalFormatting sqref="I2:I129">
+    <cfRule type="expression" priority="5" dxfId="1">
+      <formula>AND($I2&lt;&gt;"",$G2="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="5">
     <dataValidation sqref="B2:B129" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list." type="list">
       <formula1>=LISTS!$A$2:$A$10</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J129" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list." type="list">
+    <dataValidation sqref="K2:K129" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list." type="list">
       <formula1>=LISTS!$B$2:$B$3</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K129" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list." type="list">
+    <dataValidation sqref="L2:L129" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list." type="list">
       <formula1>=LISTS!$C$2:$C$3</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M129" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list." type="list">
+    <dataValidation sqref="N2:N129" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list." type="list">
       <formula1>=LISTS!$D$2:$D$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I129" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list." type="list">
+      <formula1>=LISTS!$F$2:$F$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8112,6 +8284,352 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>RMU_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>WAY</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>DIRECTION</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>NORMALLY</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>LABEL</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>NOTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>RMU-KOTE-ROAD</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>ODin</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E2" s="18" t="inlineStr"/>
+      <c r="F2" s="18" t="inlineStr">
+        <is>
+          <t>Incoming way - the RMU's own PARENT_ID is this link</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>RMU-KOTE-ROAD</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>ODout</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E3" s="19" t="inlineStr"/>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>A child of this RMU names this way in NODES!WAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>RMU-KOTE-ROAD</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>VL1</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="inlineStr"/>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>A child of this RMU names this way in NODES!WAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>RMU-KOTE-ROAD</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>VL2</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="inlineStr"/>
+      <c r="F5" s="19" t="inlineStr">
+        <is>
+          <t>A child of this RMU names this way in NODES!WAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>RMU-KOTE-ROAD</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>VL3</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="inlineStr"/>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>A child of this RMU names this way in NODES!WAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>RMU-GANGOTHTI-COLLEGE</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>ODin</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr"/>
+      <c r="F7" s="19" t="inlineStr">
+        <is>
+          <t>Incoming way - the RMU's own PARENT_ID is this link</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>RMU-GANGOTHTI-COLLEGE</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>ODout</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="inlineStr"/>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>A child of this RMU names this way in NODES!WAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>RMU-GANGOTHTI-COLLEGE</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>VL1</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr"/>
+      <c r="F9" s="19" t="inlineStr">
+        <is>
+          <t>A child of this RMU names this way in NODES!WAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>RMU-GANGOTHTI-COLLEGE</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>VL2</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="inlineStr"/>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>A child of this RMU names this way in NODES!WAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>RMU-GANGOTHTI-COLLEGE</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>VL3</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="inlineStr"/>
+      <c r="F11" s="19" t="inlineStr">
+        <is>
+          <t>A child of this RMU names this way in NODES!WAY</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F11"/>
+  <dataValidations count="3">
+    <dataValidation sqref="B2:B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list." type="list">
+      <formula1>=LISTS!$E$2:$E$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list." type="list">
+      <formula1>=LISTS!$G$2:$G$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list." type="list">
+      <formula1>=LISTS!$C$2:$C$3</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -8156,7 +8674,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>Add one row per bend on a span, SEQ = 1, 2, 3 ... along the line.</t>
         </is>
@@ -8166,721 +8684,6 @@
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="7" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="52" customWidth="1" min="14" max="14"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="B1" s="19" t="inlineStr">
-        <is>
-          <t>EXAMPLE  -  a small feeder, filled in the required format</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="B2" s="20" t="inlineStr">
-        <is>
-          <t>The trunk runs MUSS -&gt; P-001 -&gt; GOS-01 -&gt; P-002 -&gt; RMU -&gt; P-003. SCD-01 taps P-001. Spur S1 leaves the trunk at P-002 and feeds SCD-07. Every row's PARENT_ID points upstream; SPUR_ID groups the branch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>NODE_ID</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>TYPE</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>NAME</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>FEEDER</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>LAT</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>PARENT_ID</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>SPUR_ID</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>KVA</t>
-        </is>
-      </c>
-      <c r="J4" s="7" t="inlineStr">
-        <is>
-          <t>PHASE</t>
-        </is>
-      </c>
-      <c r="K4" s="7" t="inlineStr">
-        <is>
-          <t>NORMALLY</t>
-        </is>
-      </c>
-      <c r="L4" s="7" t="inlineStr">
-        <is>
-          <t>CONDUCTOR</t>
-        </is>
-      </c>
-      <c r="M4" s="7" t="inlineStr">
-        <is>
-          <t>BASIS</t>
-        </is>
-      </c>
-      <c r="N4" s="7" t="inlineStr">
-        <is>
-          <t>REMARKS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>MUSS-DEMO</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>MUSS</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>110/11KV DEMO MUSS</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>DEMO</t>
-        </is>
-      </c>
-      <c r="E5" s="15" t="n">
-        <v>13.93</v>
-      </c>
-      <c r="F5" s="15" t="n">
-        <v>75.58499999999999</v>
-      </c>
-      <c r="G5" s="12" t="inlineStr"/>
-      <c r="H5" s="13" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I5" s="13" t="n"/>
-      <c r="J5" s="13" t="inlineStr"/>
-      <c r="K5" s="13" t="inlineStr"/>
-      <c r="L5" s="12" t="inlineStr"/>
-      <c r="M5" s="13" t="inlineStr">
-        <is>
-          <t>SURVEYED</t>
-        </is>
-      </c>
-      <c r="N5" s="14" t="inlineStr">
-        <is>
-          <t>Root - no parent</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>P-001</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>POLE</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>Pole 1</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>DEMO</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>13.9298</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>75.5848</v>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>MUSS-DEMO</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I6" s="9" t="n"/>
-      <c r="J6" s="9" t="inlineStr"/>
-      <c r="K6" s="9" t="inlineStr"/>
-      <c r="L6" s="8" t="inlineStr">
-        <is>
-          <t>3x95 ABC</t>
-        </is>
-      </c>
-      <c r="M6" s="9" t="inlineStr">
-        <is>
-          <t>SURVEYED</t>
-        </is>
-      </c>
-      <c r="N6" s="10" t="inlineStr"/>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>GOS-01</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>GOS</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>DEMO GOS</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>DEMO</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>13.9296</v>
-      </c>
-      <c r="F7" s="15" t="n">
-        <v>75.58459999999999</v>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>P-001</t>
-        </is>
-      </c>
-      <c r="H7" s="13" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I7" s="13" t="n"/>
-      <c r="J7" s="13" t="inlineStr"/>
-      <c r="K7" s="13" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="L7" s="12" t="inlineStr">
-        <is>
-          <t>3x95 ABC</t>
-        </is>
-      </c>
-      <c r="M7" s="13" t="inlineStr">
-        <is>
-          <t>SURVEYED</t>
-        </is>
-      </c>
-      <c r="N7" s="14" t="inlineStr">
-        <is>
-          <t>Normally closed</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>SCD-01</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>DTC</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>GANESHA TC</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>DEMO</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>13.92955</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>75.58454999999999</v>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>P-001</t>
-        </is>
-      </c>
-      <c r="H8" s="9" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I8" s="9" t="n">
-        <v>250</v>
-      </c>
-      <c r="J8" s="9" t="inlineStr">
-        <is>
-          <t>3PH</t>
-        </is>
-      </c>
-      <c r="K8" s="9" t="inlineStr"/>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t>3x25 ABC</t>
-        </is>
-      </c>
-      <c r="M8" s="9" t="inlineStr">
-        <is>
-          <t>SURVEYED</t>
-        </is>
-      </c>
-      <c r="N8" s="10" t="inlineStr">
-        <is>
-          <t>Tap off P-001, 30 m service</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>P-002</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>POLE</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>Pole 2</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>DEMO</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>13.9293</v>
-      </c>
-      <c r="F9" s="15" t="n">
-        <v>75.5843</v>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>GOS-01</t>
-        </is>
-      </c>
-      <c r="H9" s="13" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I9" s="13" t="n"/>
-      <c r="J9" s="13" t="inlineStr"/>
-      <c r="K9" s="13" t="inlineStr"/>
-      <c r="L9" s="12" t="inlineStr">
-        <is>
-          <t>3x95 ABC</t>
-        </is>
-      </c>
-      <c r="M9" s="13" t="inlineStr">
-        <is>
-          <t>SURVEYED</t>
-        </is>
-      </c>
-      <c r="N9" s="14" t="inlineStr">
-        <is>
-          <t>Branch point for S1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>P-010</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>POLE</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>Branch pole</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>DEMO</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="n">
-        <v>13.92925</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>75.58425</v>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>P-002</t>
-        </is>
-      </c>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="I10" s="9" t="n"/>
-      <c r="J10" s="9" t="inlineStr"/>
-      <c r="K10" s="9" t="inlineStr"/>
-      <c r="L10" s="8" t="inlineStr">
-        <is>
-          <t>3x95 ABC</t>
-        </is>
-      </c>
-      <c r="M10" s="9" t="inlineStr">
-        <is>
-          <t>SURVEYED</t>
-        </is>
-      </c>
-      <c r="N10" s="10" t="inlineStr">
-        <is>
-          <t>First pole of spur S1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>SCD-07</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>DTC</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>TEMPLE STREET</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>DEMO</t>
-        </is>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>13.9292</v>
-      </c>
-      <c r="F11" s="15" t="n">
-        <v>75.5842</v>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>P-010</t>
-        </is>
-      </c>
-      <c r="H11" s="13" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="I11" s="13" t="n">
-        <v>63</v>
-      </c>
-      <c r="J11" s="13" t="inlineStr">
-        <is>
-          <t>3PH</t>
-        </is>
-      </c>
-      <c r="K11" s="13" t="inlineStr"/>
-      <c r="L11" s="12" t="inlineStr">
-        <is>
-          <t>3x25 ABC</t>
-        </is>
-      </c>
-      <c r="M11" s="13" t="inlineStr">
-        <is>
-          <t>SURVEYED</t>
-        </is>
-      </c>
-      <c r="N11" s="14" t="inlineStr"/>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>RMU-DEMO</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>RMU</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>DEMO RMU</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>DEMO</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="n">
-        <v>13.92935</v>
-      </c>
-      <c r="F12" s="11" t="n">
-        <v>75.58435</v>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>P-002</t>
-        </is>
-      </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I12" s="9" t="n"/>
-      <c r="J12" s="9" t="inlineStr"/>
-      <c r="K12" s="9" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="L12" s="8" t="inlineStr">
-        <is>
-          <t>3x95 ABC</t>
-        </is>
-      </c>
-      <c r="M12" s="9" t="inlineStr">
-        <is>
-          <t>SURVEYED</t>
-        </is>
-      </c>
-      <c r="N12" s="10" t="inlineStr">
-        <is>
-          <t>One way in from P-002, one way out to P-003</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>P-003</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>POLE</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>Pole 3</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>DEMO</t>
-        </is>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>13.929</v>
-      </c>
-      <c r="F13" s="15" t="n">
-        <v>75.584</v>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>RMU-DEMO</t>
-        </is>
-      </c>
-      <c r="H13" s="13" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="I13" s="13" t="n"/>
-      <c r="J13" s="13" t="inlineStr"/>
-      <c r="K13" s="13" t="inlineStr"/>
-      <c r="L13" s="12" t="inlineStr">
-        <is>
-          <t>3x95 ABC</t>
-        </is>
-      </c>
-      <c r="M13" s="13" t="inlineStr">
-        <is>
-          <t>SURVEYED</t>
-        </is>
-      </c>
-      <c r="N13" s="14" t="inlineStr">
-        <is>
-          <t>Continues beyond the RMU</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="21" t="inlineStr">
-        <is>
-          <t>BENDS  -  optional shape points for one span</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>FROM_ID</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>TO_ID</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>SEQ</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>LAT</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>NOTES</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>P-001</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>P-002</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="12" t="n">
-        <v>13.9297</v>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>75.5849</v>
-      </c>
-      <c r="F17" s="22" t="inlineStr">
-        <is>
-          <t>Line turns at the school corner</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>P-001</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>P-002</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>13.9295</v>
-      </c>
-      <c r="E18" s="11" t="n">
-        <v>75.5847</v>
-      </c>
-      <c r="F18" s="23" t="inlineStr">
-        <is>
-          <t>Then runs along the compound wall</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8891,13 +8694,1007 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:O27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="52" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="21" t="inlineStr">
+        <is>
+          <t>EXAMPLE  -  a small feeder, filled in the required format</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="B2" s="22" t="inlineStr">
+        <is>
+          <t>The trunk runs MUSS -&gt; P-001 -&gt; GOS-01 -&gt; P-002 -&gt; RMU (way ODin) -&gt; P-003 (way ODout). SCD-01 taps P-001 and SCD-08 leaves the RMU by way VL1. Spur S1 leaves the trunk at P-002 and feeds SCD-07. Every row's PARENT_ID points upstream; SPUR_ID groups the branch and WAY names the RMU way a child leaves by.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>NODE_ID</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>TYPE</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>NAME</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>FEEDER</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>LAT</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>PARENT_ID</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>SPUR_ID</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>WAY</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>KVA</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>PHASE</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>NORMALLY</t>
+        </is>
+      </c>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>CONDUCTOR</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="inlineStr">
+        <is>
+          <t>BASIS</t>
+        </is>
+      </c>
+      <c r="O4" s="7" t="inlineStr">
+        <is>
+          <t>REMARKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>MUSS-DEMO</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>MUSS</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>110/11KV DEMO MUSS</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>13.93</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>75.58499999999999</v>
+      </c>
+      <c r="G5" s="12" t="inlineStr"/>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="inlineStr"/>
+      <c r="J5" s="13" t="n"/>
+      <c r="K5" s="13" t="inlineStr"/>
+      <c r="L5" s="13" t="inlineStr"/>
+      <c r="M5" s="12" t="inlineStr"/>
+      <c r="N5" s="13" t="inlineStr">
+        <is>
+          <t>SURVEYED</t>
+        </is>
+      </c>
+      <c r="O5" s="14" t="inlineStr">
+        <is>
+          <t>Root - no parent</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>P-001</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>POLE</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Pole 1</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>13.9298</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>75.5848</v>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>MUSS-DEMO</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr"/>
+      <c r="J6" s="9" t="n"/>
+      <c r="K6" s="9" t="inlineStr"/>
+      <c r="L6" s="9" t="inlineStr"/>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>3x95 ABC</t>
+        </is>
+      </c>
+      <c r="N6" s="9" t="inlineStr">
+        <is>
+          <t>SURVEYED</t>
+        </is>
+      </c>
+      <c r="O6" s="10" t="inlineStr"/>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>GOS-01</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>GOS</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>DEMO GOS</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>13.9296</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>75.58459999999999</v>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>P-001</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I7" s="13" t="inlineStr"/>
+      <c r="J7" s="13" t="n"/>
+      <c r="K7" s="13" t="inlineStr"/>
+      <c r="L7" s="13" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="M7" s="12" t="inlineStr">
+        <is>
+          <t>3x95 ABC</t>
+        </is>
+      </c>
+      <c r="N7" s="13" t="inlineStr">
+        <is>
+          <t>SURVEYED</t>
+        </is>
+      </c>
+      <c r="O7" s="14" t="inlineStr">
+        <is>
+          <t>Normally closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>SCD-01</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>DTC</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>GANESHA TC</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>13.92955</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>75.58454999999999</v>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>P-001</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr"/>
+      <c r="J8" s="9" t="n">
+        <v>250</v>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>3PH</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr"/>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>3x25 ABC</t>
+        </is>
+      </c>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t>SURVEYED</t>
+        </is>
+      </c>
+      <c r="O8" s="10" t="inlineStr">
+        <is>
+          <t>Tap off P-001, 30 m service</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>P-002</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>POLE</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Pole 2</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>13.9293</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>75.5843</v>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>GOS-01</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="inlineStr"/>
+      <c r="J9" s="13" t="n"/>
+      <c r="K9" s="13" t="inlineStr"/>
+      <c r="L9" s="13" t="inlineStr"/>
+      <c r="M9" s="12" t="inlineStr">
+        <is>
+          <t>3x95 ABC</t>
+        </is>
+      </c>
+      <c r="N9" s="13" t="inlineStr">
+        <is>
+          <t>SURVEYED</t>
+        </is>
+      </c>
+      <c r="O9" s="14" t="inlineStr">
+        <is>
+          <t>Branch point for S1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>P-010</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>POLE</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Branch pole</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>13.92925</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>75.58425</v>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>P-002</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr"/>
+      <c r="J10" s="9" t="n"/>
+      <c r="K10" s="9" t="inlineStr"/>
+      <c r="L10" s="9" t="inlineStr"/>
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t>3x95 ABC</t>
+        </is>
+      </c>
+      <c r="N10" s="9" t="inlineStr">
+        <is>
+          <t>SURVEYED</t>
+        </is>
+      </c>
+      <c r="O10" s="10" t="inlineStr">
+        <is>
+          <t>First pole of spur S1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>SCD-07</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>DTC</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>TEMPLE STREET</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>13.9292</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>75.5842</v>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>P-010</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="I11" s="13" t="inlineStr"/>
+      <c r="J11" s="13" t="n">
+        <v>63</v>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>3PH</t>
+        </is>
+      </c>
+      <c r="L11" s="13" t="inlineStr"/>
+      <c r="M11" s="12" t="inlineStr">
+        <is>
+          <t>3x25 ABC</t>
+        </is>
+      </c>
+      <c r="N11" s="13" t="inlineStr">
+        <is>
+          <t>SURVEYED</t>
+        </is>
+      </c>
+      <c r="O11" s="14" t="inlineStr"/>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>RMU-DEMO</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>RMU</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>DEMO RMU</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>13.92935</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>75.58435</v>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>P-002</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr"/>
+      <c r="J12" s="9" t="n"/>
+      <c r="K12" s="9" t="inlineStr"/>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>3x95 ABC</t>
+        </is>
+      </c>
+      <c r="N12" s="9" t="inlineStr">
+        <is>
+          <t>SURVEYED</t>
+        </is>
+      </c>
+      <c r="O12" s="10" t="inlineStr">
+        <is>
+          <t>5-way unit. Fed from P-002 - that link is way ODin</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>P-003</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>POLE</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>Pole 3</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>13.929</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>75.584</v>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>RMU-DEMO</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>ODout</t>
+        </is>
+      </c>
+      <c r="J13" s="13" t="n"/>
+      <c r="K13" s="13" t="inlineStr"/>
+      <c r="L13" s="13" t="inlineStr"/>
+      <c r="M13" s="12" t="inlineStr">
+        <is>
+          <t>3x95 ABC</t>
+        </is>
+      </c>
+      <c r="N13" s="13" t="inlineStr">
+        <is>
+          <t>SURVEYED</t>
+        </is>
+      </c>
+      <c r="O13" s="14" t="inlineStr">
+        <is>
+          <t>Continues beyond the RMU by way ODout</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>SCD-08</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>DTC</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>13.92938</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>75.58432000000001</v>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>RMU-DEMO</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>VL1</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>3PH</t>
+        </is>
+      </c>
+      <c r="L14" s="9" t="inlineStr"/>
+      <c r="M14" s="8" t="inlineStr">
+        <is>
+          <t>3x25 ABC</t>
+        </is>
+      </c>
+      <c r="N14" s="9" t="inlineStr">
+        <is>
+          <t>SURVEYED</t>
+        </is>
+      </c>
+      <c r="O14" s="10" t="inlineStr">
+        <is>
+          <t>Tapped off RMU way VL1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>BENDS  -  optional shape points for one span</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>FROM_ID</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>TO_ID</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>SEQ</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>LAT</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>NOTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>P-001</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>P-002</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>13.9297</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>75.5849</v>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>Line turns at the school corner</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>P-001</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>P-002</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>13.9295</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>75.5847</v>
+      </c>
+      <c r="F19" s="19" t="inlineStr">
+        <is>
+          <t>Then runs along the compound wall</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>RMU WAYS  -  the five ways of DEMO RMU, as listed on the RMU WAYS sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>RMU_ID</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>WAY</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>DIRECTION</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>NORMALLY</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>LABEL</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>NOTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>RMU-DEMO</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>ODin</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E23" s="19" t="inlineStr">
+        <is>
+          <t>In from P-002</t>
+        </is>
+      </c>
+      <c r="F23" s="19" t="inlineStr">
+        <is>
+          <t>Fed from P-002; no child row names this way</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>RMU-DEMO</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>ODout</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E24" s="18" t="inlineStr">
+        <is>
+          <t>Out to P-003</t>
+        </is>
+      </c>
+      <c r="F24" s="18" t="inlineStr">
+        <is>
+          <t>P-003 carries WAY = ODout</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>RMU-DEMO</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>VL1</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E25" s="19" t="inlineStr"/>
+      <c r="F25" s="19" t="inlineStr">
+        <is>
+          <t>SCD-08 carries WAY = VL1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>RMU-DEMO</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>VL2</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E26" s="18" t="inlineStr"/>
+      <c r="F26" s="18" t="inlineStr">
+        <is>
+          <t>Spare way</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>RMU-DEMO</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>VL3</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E27" s="19" t="inlineStr"/>
+      <c r="F27" s="19" t="inlineStr">
+        <is>
+          <t>Spare way, normally open</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:O2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8921,6 +9718,21 @@
           <t>BASIS</t>
         </is>
       </c>
+      <c r="E1" s="24" t="inlineStr">
+        <is>
+          <t>WAY_ALL</t>
+        </is>
+      </c>
+      <c r="F1" s="24" t="inlineStr">
+        <is>
+          <t>WAY_CHILD</t>
+        </is>
+      </c>
+      <c r="G1" s="24" t="inlineStr">
+        <is>
+          <t>DIRECTION</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8943,6 +9755,21 @@
           <t>SOURCE</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ODin</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ODout</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8965,6 +9792,21 @@
           <t>INFERRED</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ODout</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VL1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8977,6 +9819,16 @@
           <t>SURVEYED</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>VL1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VL2</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8989,6 +9841,16 @@
           <t>FROM-SLD</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>VL2</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VL3</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8999,6 +9861,11 @@
       <c r="D6" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>VL3</t>
         </is>
       </c>
     </row>

--- a/template/TOPOLOGY TEMPLATE.xlsx
+++ b/template/TOPOLOGY TEMPLATE.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'NODES'!$A$1:$O$129</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'NODES'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SPURS'!$A$1:$H$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RMU WAYS'!$A$1:$F$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RMU WAYS'!$A$1:$G$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -204,7 +204,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -223,6 +223,13 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00E2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F2F2F2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -588,7 +595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B44"/>
+  <dimension ref="B1:B46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -672,10 +679,10 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="28" customHeight="1">
+    <row r="14" ht="56" customHeight="1">
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>6.  WAY is only used when the parent is an RMU. An RMU is a five-way unit - ODin, ODout, VL1, VL2, VL3 - so a child of an RMU must say which way it leaves by. Leave WAY blank everywhere else.</t>
+          <t>6.  WAY is only used when the parent is an RMU. An RMU is a five-way unit - ODin, ODout, VL1, VL2, VL3 - so a child of an RMU must say which way it leaves by. Leave WAY blank everywhere else. A unit need not use all five ways: only ODin is always cabled, and any of the four outgoing ways, ODout included, may be empty.</t>
         </is>
       </c>
     </row>
@@ -700,10 +707,10 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="42" customHeight="1">
+    <row r="19" ht="56" customHeight="1">
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>RMU WAYS One row per way of every RMU, five per unit: ODin, ODout, VL1, VL2, VL3. Records the normal state and the label of each way. Prefilled from the RMU rows in NODES; it describes the switchgear, it does not carry the connections.</t>
+          <t>RMU WAYS One row per way of every RMU, five per unit: ODin, ODout, VL1, VL2, VL3. CONNECTED says whether a cable is actually landed; the four outgoing ways start empty (N), which is normal. Records the normal state and the label of each way. Prefilled from the RMU rows in NODES; it describes the switchgear, it does not carry the connections.</t>
         </is>
       </c>
     </row>
@@ -766,7 +773,7 @@
     <row r="29" ht="28" customHeight="1">
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>•  RMU WAYS already lists all 10 ways of the 2 RMUs, normally closed. Change a way to NO only if it really sits open.</t>
+          <t>•  RMU WAYS already lists all 10 ways of the 2 RMUs: ODin cabled, the four outgoing ways marked empty. Fill in a way only where a cable really lands.</t>
         </is>
       </c>
     </row>
@@ -805,44 +812,58 @@
         </is>
       </c>
     </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Grey RMU WAYS    an empty way - no cable, nothing to draw</t>
+        </is>
+      </c>
+    </row>
     <row r="37" ht="15" customHeight="1">
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Amber NORMALLY   CONNECTED = Y but the switch state is missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>6.  WHAT TO DO FIRST</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="56" customHeight="1">
-      <c r="B38" s="4" t="inlineStr">
+    <row r="40" ht="56" customHeight="1">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>Start with MRS F1 (the largest feeder). Open the hand-drawn SLD beside this file and, for each DTC, correct PARENT_ID to the pole or DTC it actually hangs from. Add the poles you need as new rows (TYPE = POLE, NODE_ID = P-001 ...). Leave pole coordinates blank if you do not have them - the drawing will place the pole on a straight line between its neighbours, which is good enough for the topology.</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="42" customHeight="1">
-      <c r="B39" s="4" t="inlineStr">
+    <row r="41" ht="42" customHeight="1">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>When NODES is complete, the generator can be extended to draw the real trunk and spurs instead of inferring them. This workbook is the collection format; the reader is the next code step. See TOPOLOGY_DATA_REQUIREMENTS.md for the reasoning and the optional extras.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="B41" s="3" t="inlineStr">
+    <row r="43" ht="15" customHeight="1">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>7.  REBUILDING THIS TEMPLATE</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="28" customHeight="1">
-      <c r="B42" s="5" t="inlineStr">
+    <row r="44" ht="28" customHeight="1">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>python sld_generator.py --topology-template          # refuses to overwrite a filled file
 python sld_generator.py --topology-template --force  # discards your edits and rebuilds</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="28" customHeight="1">
-      <c r="B44" s="6" t="inlineStr">
+    <row r="46" ht="28" customHeight="1">
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>Coordinates are decimal degrees. Valid values for this area: lat about 13.9, long about 75.5. A latitude of 3.9 means a dropped leading digit.</t>
         </is>
@@ -1091,7 +1112,7 @@
       </c>
       <c r="O4" s="10" t="inlineStr">
         <is>
-          <t>5-way RMU: ODin, ODout, VL1, VL2, VL3. Set PARENT_ID = the node it is fed from (that link is way ODin); each child names its way in WAY. See the RMU WAYS sheet</t>
+          <t>5-way RMU: ODin, ODout, VL1, VL2, VL3 - not all need be used. Set PARENT_ID = the node it is fed from (that link is way ODin); each child names its way in WAY. See the RMU WAYS sheet</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1161,7 @@
       </c>
       <c r="O5" s="14" t="inlineStr">
         <is>
-          <t>5-way RMU: ODin, ODout, VL1, VL2, VL3. Set PARENT_ID = the node it is fed from (that link is way ODin); each child names its way in WAY. See the RMU WAYS sheet</t>
+          <t>5-way RMU: ODin, ODout, VL1, VL2, VL3 - not all need be used. Set PARENT_ID = the node it is fed from (that link is way ODin); each child names its way in WAY. See the RMU WAYS sheet</t>
         </is>
       </c>
     </row>
@@ -8284,15 +8305,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="56" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="56" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -8313,21 +8335,26 @@
       </c>
       <c r="D1" s="7" t="inlineStr">
         <is>
+          <t>CONNECTED</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
           <t>NORMALLY</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>LABEL</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1">
+    <row r="2" ht="27" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>RMU-KOTE-ROAD</t>
@@ -8345,17 +8372,22 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="E2" s="18" t="inlineStr"/>
-      <c r="F2" s="18" t="inlineStr">
-        <is>
-          <t>Incoming way - the RMU's own PARENT_ID is this link</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1">
+      <c r="F2" s="18" t="inlineStr"/>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>Incoming way, always cabled - the RMU's own PARENT_ID is this link</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="27" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>RMU-KOTE-ROAD</t>
@@ -8373,243 +8405,266 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr"/>
+      <c r="F3" s="19" t="inlineStr"/>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>Empty is normal: set CONNECTED = Y only when a cable is landed and a child row names this way in NODES!WAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="27" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>RMU-KOTE-ROAD</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>VL1</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr"/>
+      <c r="F4" s="18" t="inlineStr"/>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Empty is normal: set CONNECTED = Y only when a cable is landed and a child row names this way in NODES!WAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="27" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>RMU-KOTE-ROAD</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>VL2</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr"/>
+      <c r="F5" s="19" t="inlineStr"/>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>Empty is normal: set CONNECTED = Y only when a cable is landed and a child row names this way in NODES!WAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>RMU-KOTE-ROAD</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>VL3</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr"/>
+      <c r="F6" s="18" t="inlineStr"/>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>Empty is normal: set CONNECTED = Y only when a cable is landed and a child row names this way in NODES!WAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="27" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>RMU-GANGOTHTI-COLLEGE</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>ODin</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr"/>
-      <c r="F3" s="19" t="inlineStr">
-        <is>
-          <t>A child of this RMU names this way in NODES!WAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>RMU-KOTE-ROAD</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="F7" s="19" t="inlineStr"/>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>Incoming way, always cabled - the RMU's own PARENT_ID is this link</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>RMU-GANGOTHTI-COLLEGE</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>ODout</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr"/>
+      <c r="F8" s="18" t="inlineStr"/>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>Empty is normal: set CONNECTED = Y only when a cable is landed and a child row names this way in NODES!WAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="27" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>RMU-GANGOTHTI-COLLEGE</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>VL1</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E4" s="18" t="inlineStr"/>
-      <c r="F4" s="18" t="inlineStr">
-        <is>
-          <t>A child of this RMU names this way in NODES!WAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>RMU-KOTE-ROAD</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr"/>
+      <c r="F9" s="19" t="inlineStr"/>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>Empty is normal: set CONNECTED = Y only when a cable is landed and a child row names this way in NODES!WAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>RMU-GANGOTHTI-COLLEGE</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>VL2</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E5" s="19" t="inlineStr"/>
-      <c r="F5" s="19" t="inlineStr">
-        <is>
-          <t>A child of this RMU names this way in NODES!WAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>RMU-KOTE-ROAD</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr"/>
+      <c r="F10" s="18" t="inlineStr"/>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Empty is normal: set CONNECTED = Y only when a cable is landed and a child row names this way in NODES!WAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="27" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>RMU-GANGOTHTI-COLLEGE</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>VL3</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr"/>
-      <c r="F6" s="18" t="inlineStr">
-        <is>
-          <t>A child of this RMU names this way in NODES!WAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>RMU-GANGOTHTI-COLLEGE</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>ODin</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E7" s="19" t="inlineStr"/>
-      <c r="F7" s="19" t="inlineStr">
-        <is>
-          <t>Incoming way - the RMU's own PARENT_ID is this link</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>RMU-GANGOTHTI-COLLEGE</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>ODout</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr"/>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>A child of this RMU names this way in NODES!WAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>RMU-GANGOTHTI-COLLEGE</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>VL1</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E9" s="19" t="inlineStr"/>
-      <c r="F9" s="19" t="inlineStr">
-        <is>
-          <t>A child of this RMU names this way in NODES!WAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>RMU-GANGOTHTI-COLLEGE</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>VL2</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr"/>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>A child of this RMU names this way in NODES!WAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>RMU-GANGOTHTI-COLLEGE</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>VL3</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E11" s="19" t="inlineStr"/>
-      <c r="F11" s="19" t="inlineStr">
-        <is>
-          <t>A child of this RMU names this way in NODES!WAY</t>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr"/>
+      <c r="F11" s="19" t="inlineStr"/>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>Empty is normal: set CONNECTED = Y only when a cable is landed and a child row names this way in NODES!WAY</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F11"/>
-  <dataValidations count="3">
+  <autoFilter ref="A1:G11"/>
+  <conditionalFormatting sqref="A2:G11">
+    <cfRule type="expression" priority="1" dxfId="3">
+      <formula>$D2="N"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E11">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>AND($D2="Y",$E2="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="4">
     <dataValidation sqref="B2:B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list." type="list">
       <formula1>=LISTS!$E$2:$E$6</formula1>
     </dataValidation>
@@ -8617,6 +8672,9 @@
       <formula1>=LISTS!$G$2:$G$3</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list." type="list">
+      <formula1>=LISTS!$H$2:$H$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list." type="list">
       <formula1>=LISTS!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
@@ -8724,7 +8782,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="22" t="inlineStr">
         <is>
-          <t>The trunk runs MUSS -&gt; P-001 -&gt; GOS-01 -&gt; P-002 -&gt; RMU (way ODin) -&gt; P-003 (way ODout). SCD-01 taps P-001 and SCD-08 leaves the RMU by way VL1. Spur S1 leaves the trunk at P-002 and feeds SCD-07. Every row's PARENT_ID points upstream; SPUR_ID groups the branch and WAY names the RMU way a child leaves by.</t>
+          <t>The trunk runs MUSS -&gt; P-001 -&gt; GOS-01 -&gt; P-002 -&gt; RMU (way ODin) -&gt; P-003 (way VL2). SCD-08 leaves the RMU by way VL1; ODout and VL3 are empty. SCD-01 taps P-001. Spur S1 leaves the trunk at P-002 and feeds SCD-07. Every row's PARENT_ID points upstream; SPUR_ID groups the branch and WAY names the RMU way a child leaves by.</t>
         </is>
       </c>
     </row>
@@ -9265,7 +9323,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
+    <row r="13" ht="27" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
           <t>P-003</t>
@@ -9304,7 +9362,7 @@
       </c>
       <c r="I13" s="13" t="inlineStr">
         <is>
-          <t>ODout</t>
+          <t>VL2</t>
         </is>
       </c>
       <c r="J13" s="13" t="n"/>
@@ -9322,7 +9380,7 @@
       </c>
       <c r="O13" s="14" t="inlineStr">
         <is>
-          <t>Continues beyond the RMU by way ODout</t>
+          <t>Continues beyond the RMU by way VL2 - the run out is not always ODout</t>
         </is>
       </c>
     </row>
@@ -9509,15 +9567,20 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
+          <t>CONNECTED</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
           <t>NORMALLY</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>LABEL</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
@@ -9541,15 +9604,20 @@
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="E23" s="19" t="inlineStr">
+      <c r="F23" s="19" t="inlineStr">
         <is>
           <t>In from P-002</t>
         </is>
       </c>
-      <c r="F23" s="19" t="inlineStr">
+      <c r="G23" s="14" t="inlineStr">
         <is>
           <t>Fed from P-002; no child row names this way</t>
         </is>
@@ -9573,17 +9641,14 @@
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>Out to P-003</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>P-003 carries WAY = ODout</t>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr"/>
+      <c r="F24" s="18" t="inlineStr"/>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>Empty - no cable landed on this way</t>
         </is>
       </c>
     </row>
@@ -9605,17 +9670,22 @@
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="E25" s="19" t="inlineStr"/>
-      <c r="F25" s="19" t="inlineStr">
+      <c r="F25" s="19" t="inlineStr"/>
+      <c r="G25" s="14" t="inlineStr">
         <is>
           <t>SCD-08 carries WAY = VL1</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
+    <row r="26" ht="27" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
           <t>RMU-DEMO</t>
@@ -9633,13 +9703,22 @@
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="E26" s="18" t="inlineStr"/>
       <c r="F26" s="18" t="inlineStr">
         <is>
-          <t>Spare way</t>
+          <t>Out to P-003</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>P-003 carries WAY = VL2; the continuing run is not always ODout</t>
         </is>
       </c>
     </row>
@@ -9661,13 +9740,18 @@
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E27" s="19" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="inlineStr"/>
       <c r="F27" s="19" t="inlineStr">
         <is>
-          <t>Spare way, normally open</t>
+          <t>Spare</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>Empty spare way, ready for a new cable</t>
         </is>
       </c>
     </row>
@@ -9685,7 +9769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9695,6 +9779,7 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9733,6 +9818,11 @@
           <t>DIRECTION</t>
         </is>
       </c>
+      <c r="H1" s="24" t="inlineStr">
+        <is>
+          <t>YES_NO</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9770,6 +9860,11 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9805,6 +9900,11 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>OUT</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>

--- a/template/TOPOLOGY TEMPLATE.xlsx
+++ b/template/TOPOLOGY TEMPLATE.xlsx
@@ -843,7 +843,7 @@
     <row r="41" ht="42" customHeight="1">
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>When NODES is complete, the generator can be extended to draw the real trunk and spurs instead of inferring them. This workbook is the collection format; the reader is the next code step. See TOPOLOGY_DATA_REQUIREMENTS.md for the reasoning and the optional extras.</t>
+          <t>When NODES is complete, the generator can be extended to draw the real trunk and spurs instead of inferring them. This workbook is the collection format; the reader is the next code step. See docs/TOPOLOGY_DATA_REQUIREMENTS.md for the reasoning and the optional extras.</t>
         </is>
       </c>
     </row>
